--- a/docs/S4/Plan previsionnel S4.xlsx
+++ b/docs/S4/Plan previsionnel S4.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{32F3BEEB-0A6F-45C5-AD28-B618DC925D43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{951652E7-751C-47DE-94E3-190524F017D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="415" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1397,7 +1397,7 @@
     <xf numFmtId="0" fontId="4" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="158">
+  <cellXfs count="156">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1732,6 +1732,48 @@
     <xf numFmtId="166" fontId="1" fillId="14" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="10" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="46" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="46" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="46" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="46" borderId="0" xfId="8" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="46" borderId="0" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="46" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="46" borderId="0" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
     <xf numFmtId="0" fontId="32" fillId="13" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1785,52 +1827,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="10" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="46" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="46" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="46" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="46" borderId="0" xfId="8" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="46" borderId="0" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="46" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="46" borderId="0" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="50">
@@ -1886,121 +1882,6 @@
     <cellStyle name="zTexteMasqué" xfId="3" xr:uid="{26E66EE6-E33F-4D77-BAE4-0FB4F5BBF673}"/>
   </cellStyles>
   <dxfs count="76">
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="1" relativeIndent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.249977111117893"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <font>
         <color auto="1"/>
@@ -2758,6 +2639,121 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="1" relativeIndent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.249977111117893"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right/>
@@ -3118,7 +3114,7 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>13</xdr:col>
-          <xdr:colOff>210749</xdr:colOff>
+          <xdr:colOff>142875</xdr:colOff>
           <xdr:row>7</xdr:row>
           <xdr:rowOff>238125</xdr:rowOff>
         </xdr:to>
@@ -3216,6 +3212,89 @@
         </a:extLst>
       </xdr:spPr>
     </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1136314</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>200525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>618288</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>334210</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="ZoneTexte 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{968D1407-9F0F-85C8-800A-AE5CA21F8699}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1453814" y="16894341"/>
+          <a:ext cx="6801185" cy="2439737"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="fr-FR" sz="2800">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Les noms des membres du groupe sont indiqués à titre indicatif uniquement. Pour connaître la répartition réelle des tâches, veuillez consulter la fiche de suivi au format Excel.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="fr-FR" sz="1100">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -3332,7 +3411,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DD82988E-1813-40AE-BDE7-9F0200A703CB}" name="Jalons4352" displayName="Jalons4352" ref="B9:G35" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DD82988E-1813-40AE-BDE7-9F0200A703CB}" name="Jalons4352" displayName="Jalons4352" ref="B9:G35" totalsRowShown="0" headerRowDxfId="62" dataDxfId="61">
   <autoFilter ref="B9:G35" xr:uid="{29E5A880-80D5-4B65-B5FB-8FB3913D3D27}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -3342,12 +3421,12 @@
     <filterColumn colId="5" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{619BF8F6-D0F1-41AD-871D-FE0240C45A93}" name="Description du jalon" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{39BD914E-FB02-4352-846C-6D59624DC0B0}" name="Catégorie" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{D274194F-BCA0-44F3-84B2-217254EE241C}" name="Attribué à" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{8385BC6F-56EE-4363-A106-8DB0A1E4EF5A}" name="Progression" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{02926609-7B93-4B6F-BE96-92EC7A949E4B}" name="Début" dataDxfId="0" dataCellStyle="Date"/>
-    <tableColumn id="6" xr3:uid="{8FF9BE8E-04B7-4B39-AC27-D2E534204BC3}" name="Jours" dataDxfId="1" dataCellStyle="Milliers [0]"/>
+    <tableColumn id="1" xr3:uid="{619BF8F6-D0F1-41AD-871D-FE0240C45A93}" name="Description du jalon" dataDxfId="60"/>
+    <tableColumn id="2" xr3:uid="{39BD914E-FB02-4352-846C-6D59624DC0B0}" name="Catégorie" dataDxfId="59"/>
+    <tableColumn id="3" xr3:uid="{D274194F-BCA0-44F3-84B2-217254EE241C}" name="Attribué à" dataDxfId="58"/>
+    <tableColumn id="4" xr3:uid="{8385BC6F-56EE-4363-A106-8DB0A1E4EF5A}" name="Progression" dataDxfId="57"/>
+    <tableColumn id="5" xr3:uid="{02926609-7B93-4B6F-BE96-92EC7A949E4B}" name="Début" dataDxfId="56" dataCellStyle="Date"/>
+    <tableColumn id="6" xr3:uid="{8FF9BE8E-04B7-4B39-AC27-D2E534204BC3}" name="Jours" dataDxfId="55" dataCellStyle="Milliers [0]"/>
   </tableColumns>
   <tableStyleInfo name="ListeDesTâches" showFirstColumn="1" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
@@ -3359,7 +3438,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{0EDB95CA-98FE-4198-8801-690B9B480FDF}" name="Jalons435" displayName="Jalons435" ref="B9:G36" totalsRowShown="0" headerRowDxfId="62">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{0EDB95CA-98FE-4198-8801-690B9B480FDF}" name="Jalons435" displayName="Jalons435" ref="B9:G36" totalsRowShown="0" headerRowDxfId="54">
   <autoFilter ref="B9:G36" xr:uid="{29E5A880-80D5-4B65-B5FB-8FB3913D3D27}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -3369,9 +3448,9 @@
     <filterColumn colId="5" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{6E47A83D-ACD7-4EB6-9B84-5195E813945E}" name="Description du jalon" dataDxfId="61"/>
-    <tableColumn id="2" xr3:uid="{529EEF64-D037-4ACF-8CA4-0C10FE2D1FBB}" name="Catégorie" dataDxfId="60"/>
-    <tableColumn id="3" xr3:uid="{711D01BA-2785-403A-9636-CCC7E2ADA584}" name="Attribué à" dataDxfId="59"/>
+    <tableColumn id="1" xr3:uid="{6E47A83D-ACD7-4EB6-9B84-5195E813945E}" name="Description du jalon" dataDxfId="53"/>
+    <tableColumn id="2" xr3:uid="{529EEF64-D037-4ACF-8CA4-0C10FE2D1FBB}" name="Catégorie" dataDxfId="52"/>
+    <tableColumn id="3" xr3:uid="{711D01BA-2785-403A-9636-CCC7E2ADA584}" name="Attribué à" dataDxfId="51"/>
     <tableColumn id="4" xr3:uid="{62B00BEF-16BE-4692-B5E2-F287F680F2C1}" name="Progression"/>
     <tableColumn id="5" xr3:uid="{D6D72902-F68F-4E59-A714-AFFF520C647A}" name="Début" dataCellStyle="Date"/>
     <tableColumn id="6" xr3:uid="{93E698DE-286F-49ED-AA20-D0C843671DE8}" name="Jours" dataCellStyle="Milliers [0]"/>
@@ -3386,7 +3465,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{876EA49D-634E-482B-8173-880F7B761E2C}" name="Jalons43524" displayName="Jalons43524" ref="B9:G36" totalsRowShown="0" headerRowDxfId="58">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{876EA49D-634E-482B-8173-880F7B761E2C}" name="Jalons43524" displayName="Jalons43524" ref="B9:G36" totalsRowShown="0" headerRowDxfId="50">
   <autoFilter ref="B9:G36" xr:uid="{29E5A880-80D5-4B65-B5FB-8FB3913D3D27}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -3396,9 +3475,9 @@
     <filterColumn colId="5" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{0971B905-713A-4980-8BBC-DF959C2E61F9}" name="Description du jalon" dataDxfId="57"/>
-    <tableColumn id="2" xr3:uid="{4492A0B8-068F-4002-9E8D-E1F5FED367F0}" name="Catégorie" dataDxfId="56"/>
-    <tableColumn id="3" xr3:uid="{DF1A764E-7050-4528-B7F9-B6AB99372146}" name="Attribué à" dataDxfId="55"/>
+    <tableColumn id="1" xr3:uid="{0971B905-713A-4980-8BBC-DF959C2E61F9}" name="Description du jalon" dataDxfId="49"/>
+    <tableColumn id="2" xr3:uid="{4492A0B8-068F-4002-9E8D-E1F5FED367F0}" name="Catégorie" dataDxfId="48"/>
+    <tableColumn id="3" xr3:uid="{DF1A764E-7050-4528-B7F9-B6AB99372146}" name="Attribué à" dataDxfId="47"/>
     <tableColumn id="4" xr3:uid="{47C54592-75B0-4C70-BBF8-0F40483670E9}" name="Progression"/>
     <tableColumn id="5" xr3:uid="{663FB5E0-7616-4EA5-B56A-FF069E2E07D7}" name="Début" dataCellStyle="Date"/>
     <tableColumn id="6" xr3:uid="{3B766962-C06F-4E12-BE91-12AB93439874}" name="Jours" dataCellStyle="Milliers [0]"/>
@@ -3692,11 +3771,11 @@
     <row r="2" spans="1:13" ht="50.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="7"/>
       <c r="B2" s="98"/>
-      <c r="C2" s="124" t="s">
+      <c r="C2" s="138" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="124"/>
-      <c r="E2" s="124"/>
+      <c r="D2" s="138"/>
+      <c r="E2" s="138"/>
       <c r="F2" s="98"/>
       <c r="G2" s="7"/>
       <c r="H2" s="7"/>
@@ -3724,11 +3803,11 @@
     <row r="4" spans="1:13" s="8" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="7"/>
       <c r="B4" s="93"/>
-      <c r="C4" s="125" t="s">
+      <c r="C4" s="139" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="125"/>
-      <c r="E4" s="125"/>
+      <c r="D4" s="139"/>
+      <c r="E4" s="139"/>
       <c r="F4" s="93"/>
       <c r="G4" s="7"/>
       <c r="H4" s="7"/>
@@ -3741,11 +3820,11 @@
     <row r="5" spans="1:13" s="8" customFormat="1" ht="75.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="7"/>
       <c r="B5" s="93"/>
-      <c r="C5" s="125" t="s">
+      <c r="C5" s="139" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="125"/>
-      <c r="E5" s="125"/>
+      <c r="D5" s="139"/>
+      <c r="E5" s="139"/>
       <c r="F5" s="93"/>
       <c r="G5" s="7"/>
       <c r="H5" s="7"/>
@@ -3874,27 +3953,27 @@
     <row r="1" spans="1:74" ht="25.15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="1:74" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="10"/>
-      <c r="B2" s="129" t="s">
+      <c r="B2" s="143" t="s">
         <v>78</v>
       </c>
-      <c r="C2" s="129"/>
-      <c r="D2" s="129"/>
-      <c r="E2" s="129"/>
-      <c r="F2" s="129"/>
-      <c r="G2" s="129"/>
-      <c r="H2" s="129"/>
-      <c r="I2" s="130"/>
-      <c r="J2" s="130"/>
-      <c r="K2" s="130"/>
-      <c r="L2" s="130"/>
-      <c r="M2" s="130"/>
-      <c r="N2" s="130"/>
-      <c r="O2" s="131"/>
-      <c r="P2" s="131"/>
-      <c r="Q2" s="131"/>
-      <c r="R2" s="131"/>
-      <c r="S2" s="131"/>
-      <c r="T2" s="131"/>
+      <c r="C2" s="143"/>
+      <c r="D2" s="143"/>
+      <c r="E2" s="143"/>
+      <c r="F2" s="143"/>
+      <c r="G2" s="143"/>
+      <c r="H2" s="143"/>
+      <c r="I2" s="144"/>
+      <c r="J2" s="144"/>
+      <c r="K2" s="144"/>
+      <c r="L2" s="144"/>
+      <c r="M2" s="144"/>
+      <c r="N2" s="144"/>
+      <c r="O2" s="145"/>
+      <c r="P2" s="145"/>
+      <c r="Q2" s="145"/>
+      <c r="R2" s="145"/>
+      <c r="S2" s="145"/>
+      <c r="T2" s="145"/>
       <c r="U2" s="61"/>
       <c r="V2" s="61"/>
       <c r="W2" s="61"/>
@@ -3957,63 +4036,63 @@
     </row>
     <row r="4" spans="1:74" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="10"/>
-      <c r="B4" s="150" t="s">
+      <c r="B4" s="130" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="150" t="s">
+      <c r="C4" s="130" t="s">
         <v>33</v>
       </c>
-      <c r="D4" s="152"/>
+      <c r="D4" s="132"/>
       <c r="F4" s="70"/>
       <c r="G4" s="71" t="s">
         <v>30</v>
       </c>
       <c r="H4" s="69"/>
-      <c r="I4" s="132" t="s">
+      <c r="I4" s="146" t="s">
         <v>40</v>
       </c>
-      <c r="J4" s="132"/>
-      <c r="K4" s="132"/>
-      <c r="L4" s="132"/>
-      <c r="M4" s="132"/>
-      <c r="O4" s="133" t="s">
+      <c r="J4" s="146"/>
+      <c r="K4" s="146"/>
+      <c r="L4" s="146"/>
+      <c r="M4" s="146"/>
+      <c r="O4" s="147" t="s">
         <v>36</v>
       </c>
-      <c r="P4" s="133"/>
-      <c r="Q4" s="133"/>
-      <c r="R4" s="133"/>
-      <c r="S4" s="133"/>
-      <c r="U4" s="126" t="s">
+      <c r="P4" s="147"/>
+      <c r="Q4" s="147"/>
+      <c r="R4" s="147"/>
+      <c r="S4" s="147"/>
+      <c r="U4" s="140" t="s">
         <v>37</v>
       </c>
-      <c r="V4" s="126"/>
-      <c r="W4" s="126"/>
-      <c r="X4" s="126"/>
-      <c r="Y4" s="126"/>
-      <c r="AA4" s="127" t="s">
+      <c r="V4" s="140"/>
+      <c r="W4" s="140"/>
+      <c r="X4" s="140"/>
+      <c r="Y4" s="140"/>
+      <c r="AA4" s="141" t="s">
         <v>38</v>
       </c>
-      <c r="AB4" s="127"/>
-      <c r="AC4" s="127"/>
-      <c r="AD4" s="127"/>
-      <c r="AE4" s="127"/>
-      <c r="AG4" s="128" t="s">
+      <c r="AB4" s="141"/>
+      <c r="AC4" s="141"/>
+      <c r="AD4" s="141"/>
+      <c r="AE4" s="141"/>
+      <c r="AG4" s="142" t="s">
         <v>39</v>
       </c>
-      <c r="AH4" s="128"/>
-      <c r="AI4" s="128"/>
-      <c r="AJ4" s="128"/>
-      <c r="AK4" s="128"/>
+      <c r="AH4" s="142"/>
+      <c r="AI4" s="142"/>
+      <c r="AJ4" s="142"/>
+      <c r="AK4" s="142"/>
     </row>
     <row r="5" spans="1:74" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="10"/>
-      <c r="B5" s="151" t="s">
+      <c r="B5" s="131" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="152" t="s">
+      <c r="C5" s="132" t="s">
         <v>46</v>
       </c>
-      <c r="D5" s="152"/>
+      <c r="D5" s="132"/>
       <c r="E5" s="69"/>
       <c r="F5" s="70"/>
       <c r="G5" s="69"/>
@@ -4021,13 +4100,13 @@
     </row>
     <row r="6" spans="1:74" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="10"/>
-      <c r="B6" s="153" t="s">
+      <c r="B6" s="133" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="154">
+      <c r="C6" s="134">
         <v>46128</v>
       </c>
-      <c r="D6" s="157"/>
+      <c r="D6" s="137"/>
       <c r="E6" s="69"/>
       <c r="F6" s="70"/>
       <c r="G6" s="69"/>
@@ -4125,13 +4204,13 @@
     </row>
     <row r="7" spans="1:74" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="10"/>
-      <c r="B7" s="153" t="s">
+      <c r="B7" s="133" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="155">
+      <c r="C7" s="135">
         <v>1</v>
       </c>
-      <c r="D7" s="152"/>
+      <c r="D7" s="132"/>
       <c r="E7" s="69"/>
       <c r="F7" s="69"/>
       <c r="G7" s="69"/>
@@ -4819,7 +4898,7 @@
     </row>
     <row r="11" spans="1:74" s="1" customFormat="1" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A11" s="10"/>
-      <c r="B11" s="156" t="s">
+      <c r="B11" s="136" t="s">
         <v>77</v>
       </c>
       <c r="C11" s="54"/>
@@ -5056,7 +5135,7 @@
     </row>
     <row r="12" spans="1:74" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="10"/>
-      <c r="B12" s="149" t="s">
+      <c r="B12" s="129" t="s">
         <v>75</v>
       </c>
       <c r="C12" s="54" t="s">
@@ -6286,7 +6365,7 @@
     </row>
     <row r="17" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10"/>
-      <c r="B17" s="149" t="s">
+      <c r="B17" s="129" t="s">
         <v>74</v>
       </c>
       <c r="C17" s="54" t="s">
@@ -7766,7 +7845,7 @@
     </row>
     <row r="23" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="9"/>
-      <c r="B23" s="148" t="s">
+      <c r="B23" s="128" t="s">
         <v>73</v>
       </c>
       <c r="C23" s="54" t="s">
@@ -8269,7 +8348,7 @@
       </c>
       <c r="E25" s="55"/>
       <c r="F25" s="56">
-        <f>F20+22</f>
+        <f t="shared" ref="F25:F35" si="29">F20+22</f>
         <v>46182</v>
       </c>
       <c r="G25" s="57">
@@ -8277,227 +8356,227 @@
       </c>
       <c r="H25" s="54"/>
       <c r="I25" s="24" t="str">
-        <f t="shared" ref="I25:AN25" ca="1" si="29">IF(AND($C23="Objectif",I$7&gt;=$F23,I$7&lt;=$F23+$G23-1),2,IF(AND($C23="Jalon",I$7&gt;=$F23,I$7&lt;=$F23+$G23-1),1,""))</f>
+        <f t="shared" ref="I25:AN25" ca="1" si="30">IF(AND($C23="Objectif",I$7&gt;=$F23,I$7&lt;=$F23+$G23-1),2,IF(AND($C23="Jalon",I$7&gt;=$F23,I$7&lt;=$F23+$G23-1),1,""))</f>
         <v/>
       </c>
       <c r="J25" s="24" t="str">
-        <f t="shared" ca="1" si="29"/>
+        <f t="shared" ca="1" si="30"/>
         <v/>
       </c>
       <c r="K25" s="24" t="str">
-        <f t="shared" ca="1" si="29"/>
+        <f t="shared" ca="1" si="30"/>
         <v/>
       </c>
       <c r="L25" s="24" t="str">
-        <f t="shared" ca="1" si="29"/>
+        <f t="shared" ca="1" si="30"/>
         <v/>
       </c>
       <c r="M25" s="24" t="str">
-        <f t="shared" ca="1" si="29"/>
+        <f t="shared" ca="1" si="30"/>
         <v/>
       </c>
       <c r="N25" s="24" t="str">
-        <f t="shared" ca="1" si="29"/>
+        <f t="shared" ca="1" si="30"/>
         <v/>
       </c>
       <c r="O25" s="24" t="str">
-        <f t="shared" ca="1" si="29"/>
+        <f t="shared" ca="1" si="30"/>
         <v/>
       </c>
       <c r="P25" s="24" t="str">
-        <f t="shared" ca="1" si="29"/>
+        <f t="shared" ca="1" si="30"/>
         <v/>
       </c>
       <c r="Q25" s="24" t="str">
-        <f t="shared" ca="1" si="29"/>
+        <f t="shared" ca="1" si="30"/>
         <v/>
       </c>
       <c r="R25" s="24" t="str">
-        <f t="shared" ca="1" si="29"/>
+        <f t="shared" ca="1" si="30"/>
         <v/>
       </c>
       <c r="S25" s="24" t="str">
-        <f t="shared" ca="1" si="29"/>
+        <f t="shared" ca="1" si="30"/>
         <v/>
       </c>
       <c r="T25" s="24" t="str">
-        <f t="shared" ca="1" si="29"/>
+        <f t="shared" ca="1" si="30"/>
         <v/>
       </c>
       <c r="U25" s="24" t="str">
-        <f t="shared" ca="1" si="29"/>
+        <f t="shared" ca="1" si="30"/>
         <v/>
       </c>
       <c r="V25" s="24" t="str">
-        <f t="shared" ca="1" si="29"/>
+        <f t="shared" ca="1" si="30"/>
         <v/>
       </c>
       <c r="W25" s="24" t="str">
-        <f t="shared" ca="1" si="29"/>
+        <f t="shared" ca="1" si="30"/>
         <v/>
       </c>
       <c r="X25" s="24" t="str">
-        <f t="shared" ca="1" si="29"/>
+        <f t="shared" ca="1" si="30"/>
         <v/>
       </c>
       <c r="Y25" s="24" t="str">
-        <f t="shared" ca="1" si="29"/>
+        <f t="shared" ca="1" si="30"/>
         <v/>
       </c>
       <c r="Z25" s="24" t="str">
-        <f t="shared" ca="1" si="29"/>
+        <f t="shared" ca="1" si="30"/>
         <v/>
       </c>
       <c r="AA25" s="24" t="str">
-        <f t="shared" ca="1" si="29"/>
+        <f t="shared" ca="1" si="30"/>
         <v/>
       </c>
       <c r="AB25" s="24" t="str">
-        <f t="shared" ca="1" si="29"/>
+        <f t="shared" ca="1" si="30"/>
         <v/>
       </c>
       <c r="AC25" s="24" t="str">
-        <f t="shared" ca="1" si="29"/>
+        <f t="shared" ca="1" si="30"/>
         <v/>
       </c>
       <c r="AD25" s="24" t="str">
-        <f t="shared" ca="1" si="29"/>
+        <f t="shared" ca="1" si="30"/>
         <v/>
       </c>
       <c r="AE25" s="24" t="str">
-        <f t="shared" ca="1" si="29"/>
+        <f t="shared" ca="1" si="30"/>
         <v/>
       </c>
       <c r="AF25" s="24" t="str">
-        <f t="shared" ca="1" si="29"/>
+        <f t="shared" ca="1" si="30"/>
         <v/>
       </c>
       <c r="AG25" s="24" t="str">
-        <f t="shared" ca="1" si="29"/>
+        <f t="shared" ca="1" si="30"/>
         <v/>
       </c>
       <c r="AH25" s="24" t="str">
-        <f t="shared" ca="1" si="29"/>
+        <f t="shared" ca="1" si="30"/>
         <v/>
       </c>
       <c r="AI25" s="24" t="str">
-        <f t="shared" ca="1" si="29"/>
+        <f t="shared" ca="1" si="30"/>
         <v/>
       </c>
       <c r="AJ25" s="24" t="str">
-        <f t="shared" ca="1" si="29"/>
+        <f t="shared" ca="1" si="30"/>
         <v/>
       </c>
       <c r="AK25" s="24" t="str">
-        <f t="shared" ca="1" si="29"/>
+        <f t="shared" ca="1" si="30"/>
         <v/>
       </c>
       <c r="AL25" s="24" t="str">
-        <f t="shared" ca="1" si="29"/>
+        <f t="shared" ca="1" si="30"/>
         <v/>
       </c>
       <c r="AM25" s="24" t="str">
-        <f t="shared" ca="1" si="29"/>
+        <f t="shared" ca="1" si="30"/>
         <v/>
       </c>
       <c r="AN25" s="24" t="str">
-        <f t="shared" ca="1" si="29"/>
+        <f t="shared" ca="1" si="30"/>
         <v/>
       </c>
       <c r="AO25" s="24" t="str">
-        <f t="shared" ref="AO25:BL25" ca="1" si="30">IF(AND($C23="Objectif",AO$7&gt;=$F23,AO$7&lt;=$F23+$G23-1),2,IF(AND($C23="Jalon",AO$7&gt;=$F23,AO$7&lt;=$F23+$G23-1),1,""))</f>
+        <f t="shared" ref="AO25:BL25" ca="1" si="31">IF(AND($C23="Objectif",AO$7&gt;=$F23,AO$7&lt;=$F23+$G23-1),2,IF(AND($C23="Jalon",AO$7&gt;=$F23,AO$7&lt;=$F23+$G23-1),1,""))</f>
         <v/>
       </c>
       <c r="AP25" s="24" t="str">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" ca="1" si="31"/>
         <v/>
       </c>
       <c r="AQ25" s="24" t="str">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" ca="1" si="31"/>
         <v/>
       </c>
       <c r="AR25" s="24" t="str">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" ca="1" si="31"/>
         <v/>
       </c>
       <c r="AS25" s="24" t="str">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" ca="1" si="31"/>
         <v/>
       </c>
       <c r="AT25" s="24" t="str">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" ca="1" si="31"/>
         <v/>
       </c>
       <c r="AU25" s="24" t="str">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" ca="1" si="31"/>
         <v/>
       </c>
       <c r="AV25" s="24" t="str">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" ca="1" si="31"/>
         <v/>
       </c>
       <c r="AW25" s="24" t="str">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" ca="1" si="31"/>
         <v/>
       </c>
       <c r="AX25" s="24" t="str">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" ca="1" si="31"/>
         <v/>
       </c>
       <c r="AY25" s="24" t="str">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" ca="1" si="31"/>
         <v/>
       </c>
       <c r="AZ25" s="24" t="str">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" ca="1" si="31"/>
         <v/>
       </c>
       <c r="BA25" s="24" t="str">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" ca="1" si="31"/>
         <v/>
       </c>
       <c r="BB25" s="24" t="str">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" ca="1" si="31"/>
         <v/>
       </c>
       <c r="BC25" s="24" t="str">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" ca="1" si="31"/>
         <v/>
       </c>
       <c r="BD25" s="24" t="str">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" ca="1" si="31"/>
         <v/>
       </c>
       <c r="BE25" s="24" t="str">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" ca="1" si="31"/>
         <v/>
       </c>
       <c r="BF25" s="24" t="str">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" ca="1" si="31"/>
         <v/>
       </c>
       <c r="BG25" s="24" t="str">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" ca="1" si="31"/>
         <v/>
       </c>
       <c r="BH25" s="24" t="str">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" ca="1" si="31"/>
         <v/>
       </c>
       <c r="BI25" s="24" t="str">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" ca="1" si="31"/>
         <v/>
       </c>
       <c r="BJ25" s="24" t="str">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" ca="1" si="31"/>
         <v/>
       </c>
       <c r="BK25" s="24" t="str">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" ca="1" si="31"/>
         <v/>
       </c>
       <c r="BL25" s="24" t="str">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" ca="1" si="31"/>
         <v/>
       </c>
     </row>
@@ -8516,7 +8595,7 @@
         <v>0.5</v>
       </c>
       <c r="F26" s="56">
-        <f>F21+22</f>
+        <f t="shared" si="29"/>
         <v>46183</v>
       </c>
       <c r="G26" s="57">
@@ -8524,233 +8603,233 @@
       </c>
       <c r="H26" s="54"/>
       <c r="I26" s="24" t="str">
-        <f t="shared" ref="I26:AN26" ca="1" si="31">IF(AND($C24="Objectif",I$7&gt;=$F24,I$7&lt;=$F24+$G24-1),2,IF(AND($C24="Jalon",I$7&gt;=$F24,I$7&lt;=$F24+$G24-1),1,""))</f>
+        <f t="shared" ref="I26:AN26" ca="1" si="32">IF(AND($C24="Objectif",I$7&gt;=$F24,I$7&lt;=$F24+$G24-1),2,IF(AND($C24="Jalon",I$7&gt;=$F24,I$7&lt;=$F24+$G24-1),1,""))</f>
         <v/>
       </c>
       <c r="J26" s="24" t="str">
-        <f t="shared" ca="1" si="31"/>
+        <f t="shared" ca="1" si="32"/>
         <v/>
       </c>
       <c r="K26" s="24" t="str">
-        <f t="shared" ca="1" si="31"/>
+        <f t="shared" ca="1" si="32"/>
         <v/>
       </c>
       <c r="L26" s="24" t="str">
-        <f t="shared" ca="1" si="31"/>
+        <f t="shared" ca="1" si="32"/>
         <v/>
       </c>
       <c r="M26" s="24" t="str">
-        <f t="shared" ca="1" si="31"/>
+        <f t="shared" ca="1" si="32"/>
         <v/>
       </c>
       <c r="N26" s="24" t="str">
-        <f t="shared" ca="1" si="31"/>
+        <f t="shared" ca="1" si="32"/>
         <v/>
       </c>
       <c r="O26" s="24" t="str">
-        <f t="shared" ca="1" si="31"/>
+        <f t="shared" ca="1" si="32"/>
         <v/>
       </c>
       <c r="P26" s="24" t="str">
-        <f t="shared" ca="1" si="31"/>
+        <f t="shared" ca="1" si="32"/>
         <v/>
       </c>
       <c r="Q26" s="24" t="str">
-        <f t="shared" ca="1" si="31"/>
+        <f t="shared" ca="1" si="32"/>
         <v/>
       </c>
       <c r="R26" s="24" t="str">
-        <f t="shared" ca="1" si="31"/>
+        <f t="shared" ca="1" si="32"/>
         <v/>
       </c>
       <c r="S26" s="24" t="str">
-        <f t="shared" ca="1" si="31"/>
+        <f t="shared" ca="1" si="32"/>
         <v/>
       </c>
       <c r="T26" s="24" t="str">
-        <f t="shared" ca="1" si="31"/>
+        <f t="shared" ca="1" si="32"/>
         <v/>
       </c>
       <c r="U26" s="24" t="str">
-        <f t="shared" ca="1" si="31"/>
+        <f t="shared" ca="1" si="32"/>
         <v/>
       </c>
       <c r="V26" s="24" t="str">
-        <f t="shared" ca="1" si="31"/>
+        <f t="shared" ca="1" si="32"/>
         <v/>
       </c>
       <c r="W26" s="24" t="str">
-        <f t="shared" ca="1" si="31"/>
+        <f t="shared" ca="1" si="32"/>
         <v/>
       </c>
       <c r="X26" s="24" t="str">
-        <f t="shared" ca="1" si="31"/>
+        <f t="shared" ca="1" si="32"/>
         <v/>
       </c>
       <c r="Y26" s="24" t="str">
-        <f t="shared" ca="1" si="31"/>
+        <f t="shared" ca="1" si="32"/>
         <v/>
       </c>
       <c r="Z26" s="24" t="str">
-        <f t="shared" ca="1" si="31"/>
+        <f t="shared" ca="1" si="32"/>
         <v/>
       </c>
       <c r="AA26" s="24" t="str">
-        <f t="shared" ca="1" si="31"/>
+        <f t="shared" ca="1" si="32"/>
         <v/>
       </c>
       <c r="AB26" s="24" t="str">
-        <f t="shared" ca="1" si="31"/>
+        <f t="shared" ca="1" si="32"/>
         <v/>
       </c>
       <c r="AC26" s="24" t="str">
-        <f t="shared" ca="1" si="31"/>
+        <f t="shared" ca="1" si="32"/>
         <v/>
       </c>
       <c r="AD26" s="24" t="str">
-        <f t="shared" ca="1" si="31"/>
+        <f t="shared" ca="1" si="32"/>
         <v/>
       </c>
       <c r="AE26" s="24" t="str">
-        <f t="shared" ca="1" si="31"/>
+        <f t="shared" ca="1" si="32"/>
         <v/>
       </c>
       <c r="AF26" s="24" t="str">
-        <f t="shared" ca="1" si="31"/>
+        <f t="shared" ca="1" si="32"/>
         <v/>
       </c>
       <c r="AG26" s="24" t="str">
-        <f t="shared" ca="1" si="31"/>
+        <f t="shared" ca="1" si="32"/>
         <v/>
       </c>
       <c r="AH26" s="24" t="str">
-        <f t="shared" ca="1" si="31"/>
+        <f t="shared" ca="1" si="32"/>
         <v/>
       </c>
       <c r="AI26" s="24" t="str">
-        <f t="shared" ca="1" si="31"/>
+        <f t="shared" ca="1" si="32"/>
         <v/>
       </c>
       <c r="AJ26" s="24" t="str">
-        <f t="shared" ca="1" si="31"/>
+        <f t="shared" ca="1" si="32"/>
         <v/>
       </c>
       <c r="AK26" s="24" t="str">
-        <f t="shared" ca="1" si="31"/>
+        <f t="shared" ca="1" si="32"/>
         <v/>
       </c>
       <c r="AL26" s="24" t="str">
-        <f t="shared" ca="1" si="31"/>
+        <f t="shared" ca="1" si="32"/>
         <v/>
       </c>
       <c r="AM26" s="24" t="str">
-        <f t="shared" ca="1" si="31"/>
+        <f t="shared" ca="1" si="32"/>
         <v/>
       </c>
       <c r="AN26" s="24" t="str">
-        <f t="shared" ca="1" si="31"/>
+        <f t="shared" ca="1" si="32"/>
         <v/>
       </c>
       <c r="AO26" s="24" t="str">
-        <f t="shared" ref="AO26:BL26" ca="1" si="32">IF(AND($C24="Objectif",AO$7&gt;=$F24,AO$7&lt;=$F24+$G24-1),2,IF(AND($C24="Jalon",AO$7&gt;=$F24,AO$7&lt;=$F24+$G24-1),1,""))</f>
+        <f t="shared" ref="AO26:BL26" ca="1" si="33">IF(AND($C24="Objectif",AO$7&gt;=$F24,AO$7&lt;=$F24+$G24-1),2,IF(AND($C24="Jalon",AO$7&gt;=$F24,AO$7&lt;=$F24+$G24-1),1,""))</f>
         <v/>
       </c>
       <c r="AP26" s="24" t="str">
-        <f t="shared" ca="1" si="32"/>
+        <f t="shared" ca="1" si="33"/>
         <v/>
       </c>
       <c r="AQ26" s="24" t="str">
-        <f t="shared" ca="1" si="32"/>
+        <f t="shared" ca="1" si="33"/>
         <v/>
       </c>
       <c r="AR26" s="24" t="str">
-        <f t="shared" ca="1" si="32"/>
+        <f t="shared" ca="1" si="33"/>
         <v/>
       </c>
       <c r="AS26" s="24" t="str">
-        <f t="shared" ca="1" si="32"/>
+        <f t="shared" ca="1" si="33"/>
         <v/>
       </c>
       <c r="AT26" s="24" t="str">
-        <f t="shared" ca="1" si="32"/>
+        <f t="shared" ca="1" si="33"/>
         <v/>
       </c>
       <c r="AU26" s="24" t="str">
-        <f t="shared" ca="1" si="32"/>
+        <f t="shared" ca="1" si="33"/>
         <v/>
       </c>
       <c r="AV26" s="24" t="str">
-        <f t="shared" ca="1" si="32"/>
+        <f t="shared" ca="1" si="33"/>
         <v/>
       </c>
       <c r="AW26" s="24" t="str">
-        <f t="shared" ca="1" si="32"/>
+        <f t="shared" ca="1" si="33"/>
         <v/>
       </c>
       <c r="AX26" s="24" t="str">
-        <f t="shared" ca="1" si="32"/>
+        <f t="shared" ca="1" si="33"/>
         <v/>
       </c>
       <c r="AY26" s="24" t="str">
-        <f t="shared" ca="1" si="32"/>
+        <f t="shared" ca="1" si="33"/>
         <v/>
       </c>
       <c r="AZ26" s="24" t="str">
-        <f t="shared" ca="1" si="32"/>
+        <f t="shared" ca="1" si="33"/>
         <v/>
       </c>
       <c r="BA26" s="24" t="str">
-        <f t="shared" ca="1" si="32"/>
+        <f t="shared" ca="1" si="33"/>
         <v/>
       </c>
       <c r="BB26" s="24" t="str">
-        <f t="shared" ca="1" si="32"/>
+        <f t="shared" ca="1" si="33"/>
         <v/>
       </c>
       <c r="BC26" s="24" t="str">
-        <f t="shared" ca="1" si="32"/>
+        <f t="shared" ca="1" si="33"/>
         <v/>
       </c>
       <c r="BD26" s="24" t="str">
-        <f t="shared" ca="1" si="32"/>
+        <f t="shared" ca="1" si="33"/>
         <v/>
       </c>
       <c r="BE26" s="24" t="str">
-        <f t="shared" ca="1" si="32"/>
+        <f t="shared" ca="1" si="33"/>
         <v/>
       </c>
       <c r="BF26" s="24" t="str">
-        <f t="shared" ca="1" si="32"/>
+        <f t="shared" ca="1" si="33"/>
         <v/>
       </c>
       <c r="BG26" s="24" t="str">
-        <f t="shared" ca="1" si="32"/>
+        <f t="shared" ca="1" si="33"/>
         <v/>
       </c>
       <c r="BH26" s="24" t="str">
-        <f t="shared" ca="1" si="32"/>
+        <f t="shared" ca="1" si="33"/>
         <v/>
       </c>
       <c r="BI26" s="24" t="str">
-        <f t="shared" ca="1" si="32"/>
+        <f t="shared" ca="1" si="33"/>
         <v/>
       </c>
       <c r="BJ26" s="24" t="str">
-        <f t="shared" ca="1" si="32"/>
+        <f t="shared" ca="1" si="33"/>
         <v/>
       </c>
       <c r="BK26" s="24" t="str">
-        <f t="shared" ca="1" si="32"/>
+        <f t="shared" ca="1" si="33"/>
         <v/>
       </c>
       <c r="BL26" s="24" t="str">
-        <f t="shared" ca="1" si="32"/>
+        <f t="shared" ca="1" si="33"/>
         <v/>
       </c>
     </row>
     <row r="27" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="9"/>
-      <c r="B27" s="147" t="s">
+      <c r="B27" s="127" t="s">
         <v>72</v>
       </c>
       <c r="C27" s="54" t="s">
@@ -8761,7 +8840,7 @@
       </c>
       <c r="E27" s="55"/>
       <c r="F27" s="56">
-        <f>F22+22</f>
+        <f t="shared" si="29"/>
         <v>46165</v>
       </c>
       <c r="G27" s="57">
@@ -8769,227 +8848,227 @@
       </c>
       <c r="H27" s="54"/>
       <c r="I27" s="24" t="str">
-        <f t="shared" ref="I27:AN27" ca="1" si="33">IF(AND($C25="Objectif",I$7&gt;=$F25,I$7&lt;=$F25+$G25-1),2,IF(AND($C25="Jalon",I$7&gt;=$F25,I$7&lt;=$F25+$G25-1),1,""))</f>
+        <f t="shared" ref="I27:AN27" ca="1" si="34">IF(AND($C25="Objectif",I$7&gt;=$F25,I$7&lt;=$F25+$G25-1),2,IF(AND($C25="Jalon",I$7&gt;=$F25,I$7&lt;=$F25+$G25-1),1,""))</f>
         <v/>
       </c>
       <c r="J27" s="24" t="str">
-        <f t="shared" ca="1" si="33"/>
+        <f t="shared" ca="1" si="34"/>
         <v/>
       </c>
       <c r="K27" s="24" t="str">
-        <f t="shared" ca="1" si="33"/>
+        <f t="shared" ca="1" si="34"/>
         <v/>
       </c>
       <c r="L27" s="24" t="str">
-        <f t="shared" ca="1" si="33"/>
+        <f t="shared" ca="1" si="34"/>
         <v/>
       </c>
       <c r="M27" s="24" t="str">
-        <f t="shared" ca="1" si="33"/>
+        <f t="shared" ca="1" si="34"/>
         <v/>
       </c>
       <c r="N27" s="24" t="str">
-        <f t="shared" ca="1" si="33"/>
+        <f t="shared" ca="1" si="34"/>
         <v/>
       </c>
       <c r="O27" s="24" t="str">
-        <f t="shared" ca="1" si="33"/>
+        <f t="shared" ca="1" si="34"/>
         <v/>
       </c>
       <c r="P27" s="24" t="str">
-        <f t="shared" ca="1" si="33"/>
+        <f t="shared" ca="1" si="34"/>
         <v/>
       </c>
       <c r="Q27" s="24" t="str">
-        <f t="shared" ca="1" si="33"/>
+        <f t="shared" ca="1" si="34"/>
         <v/>
       </c>
       <c r="R27" s="24" t="str">
-        <f t="shared" ca="1" si="33"/>
+        <f t="shared" ca="1" si="34"/>
         <v/>
       </c>
       <c r="S27" s="24" t="str">
-        <f t="shared" ca="1" si="33"/>
+        <f t="shared" ca="1" si="34"/>
         <v/>
       </c>
       <c r="T27" s="24" t="str">
-        <f t="shared" ca="1" si="33"/>
+        <f t="shared" ca="1" si="34"/>
         <v/>
       </c>
       <c r="U27" s="24" t="str">
-        <f t="shared" ca="1" si="33"/>
+        <f t="shared" ca="1" si="34"/>
         <v/>
       </c>
       <c r="V27" s="24" t="str">
-        <f t="shared" ca="1" si="33"/>
+        <f t="shared" ca="1" si="34"/>
         <v/>
       </c>
       <c r="W27" s="24" t="str">
-        <f t="shared" ca="1" si="33"/>
+        <f t="shared" ca="1" si="34"/>
         <v/>
       </c>
       <c r="X27" s="24" t="str">
-        <f t="shared" ca="1" si="33"/>
+        <f t="shared" ca="1" si="34"/>
         <v/>
       </c>
       <c r="Y27" s="24" t="str">
-        <f t="shared" ca="1" si="33"/>
+        <f t="shared" ca="1" si="34"/>
         <v/>
       </c>
       <c r="Z27" s="24" t="str">
-        <f t="shared" ca="1" si="33"/>
+        <f t="shared" ca="1" si="34"/>
         <v/>
       </c>
       <c r="AA27" s="24" t="str">
-        <f t="shared" ca="1" si="33"/>
+        <f t="shared" ca="1" si="34"/>
         <v/>
       </c>
       <c r="AB27" s="24" t="str">
-        <f t="shared" ca="1" si="33"/>
+        <f t="shared" ca="1" si="34"/>
         <v/>
       </c>
       <c r="AC27" s="24" t="str">
-        <f t="shared" ca="1" si="33"/>
+        <f t="shared" ca="1" si="34"/>
         <v/>
       </c>
       <c r="AD27" s="24" t="str">
-        <f t="shared" ca="1" si="33"/>
+        <f t="shared" ca="1" si="34"/>
         <v/>
       </c>
       <c r="AE27" s="24" t="str">
-        <f t="shared" ca="1" si="33"/>
+        <f t="shared" ca="1" si="34"/>
         <v/>
       </c>
       <c r="AF27" s="24" t="str">
-        <f t="shared" ca="1" si="33"/>
+        <f t="shared" ca="1" si="34"/>
         <v/>
       </c>
       <c r="AG27" s="24" t="str">
-        <f t="shared" ca="1" si="33"/>
+        <f t="shared" ca="1" si="34"/>
         <v/>
       </c>
       <c r="AH27" s="24" t="str">
-        <f t="shared" ca="1" si="33"/>
+        <f t="shared" ca="1" si="34"/>
         <v/>
       </c>
       <c r="AI27" s="24" t="str">
-        <f t="shared" ca="1" si="33"/>
+        <f t="shared" ca="1" si="34"/>
         <v/>
       </c>
       <c r="AJ27" s="24" t="str">
-        <f t="shared" ca="1" si="33"/>
+        <f t="shared" ca="1" si="34"/>
         <v/>
       </c>
       <c r="AK27" s="24" t="str">
-        <f t="shared" ca="1" si="33"/>
+        <f t="shared" ca="1" si="34"/>
         <v/>
       </c>
       <c r="AL27" s="24" t="str">
-        <f t="shared" ca="1" si="33"/>
+        <f t="shared" ca="1" si="34"/>
         <v/>
       </c>
       <c r="AM27" s="24" t="str">
-        <f t="shared" ca="1" si="33"/>
+        <f t="shared" ca="1" si="34"/>
         <v/>
       </c>
       <c r="AN27" s="24" t="str">
-        <f t="shared" ca="1" si="33"/>
+        <f t="shared" ca="1" si="34"/>
         <v/>
       </c>
       <c r="AO27" s="24" t="str">
-        <f t="shared" ref="AO27:BL27" ca="1" si="34">IF(AND($C25="Objectif",AO$7&gt;=$F25,AO$7&lt;=$F25+$G25-1),2,IF(AND($C25="Jalon",AO$7&gt;=$F25,AO$7&lt;=$F25+$G25-1),1,""))</f>
+        <f t="shared" ref="AO27:BL27" ca="1" si="35">IF(AND($C25="Objectif",AO$7&gt;=$F25,AO$7&lt;=$F25+$G25-1),2,IF(AND($C25="Jalon",AO$7&gt;=$F25,AO$7&lt;=$F25+$G25-1),1,""))</f>
         <v/>
       </c>
       <c r="AP27" s="24" t="str">
-        <f t="shared" ca="1" si="34"/>
+        <f t="shared" ca="1" si="35"/>
         <v/>
       </c>
       <c r="AQ27" s="24" t="str">
-        <f t="shared" ca="1" si="34"/>
+        <f t="shared" ca="1" si="35"/>
         <v/>
       </c>
       <c r="AR27" s="24" t="str">
-        <f t="shared" ca="1" si="34"/>
+        <f t="shared" ca="1" si="35"/>
         <v/>
       </c>
       <c r="AS27" s="24" t="str">
-        <f t="shared" ca="1" si="34"/>
+        <f t="shared" ca="1" si="35"/>
         <v/>
       </c>
       <c r="AT27" s="24" t="str">
-        <f t="shared" ca="1" si="34"/>
+        <f t="shared" ca="1" si="35"/>
         <v/>
       </c>
       <c r="AU27" s="24" t="str">
-        <f t="shared" ca="1" si="34"/>
+        <f t="shared" ca="1" si="35"/>
         <v/>
       </c>
       <c r="AV27" s="24" t="str">
-        <f t="shared" ca="1" si="34"/>
+        <f t="shared" ca="1" si="35"/>
         <v/>
       </c>
       <c r="AW27" s="24" t="str">
-        <f t="shared" ca="1" si="34"/>
+        <f t="shared" ca="1" si="35"/>
         <v/>
       </c>
       <c r="AX27" s="24" t="str">
-        <f t="shared" ca="1" si="34"/>
+        <f t="shared" ca="1" si="35"/>
         <v/>
       </c>
       <c r="AY27" s="24" t="str">
-        <f t="shared" ca="1" si="34"/>
+        <f t="shared" ca="1" si="35"/>
         <v/>
       </c>
       <c r="AZ27" s="24" t="str">
-        <f t="shared" ca="1" si="34"/>
+        <f t="shared" ca="1" si="35"/>
         <v/>
       </c>
       <c r="BA27" s="24" t="str">
-        <f t="shared" ca="1" si="34"/>
+        <f t="shared" ca="1" si="35"/>
         <v/>
       </c>
       <c r="BB27" s="24" t="str">
-        <f t="shared" ca="1" si="34"/>
+        <f t="shared" ca="1" si="35"/>
         <v/>
       </c>
       <c r="BC27" s="24" t="str">
-        <f t="shared" ca="1" si="34"/>
+        <f t="shared" ca="1" si="35"/>
         <v/>
       </c>
       <c r="BD27" s="24" t="str">
-        <f t="shared" ca="1" si="34"/>
+        <f t="shared" ca="1" si="35"/>
         <v/>
       </c>
       <c r="BE27" s="24" t="str">
-        <f t="shared" ca="1" si="34"/>
+        <f t="shared" ca="1" si="35"/>
         <v/>
       </c>
       <c r="BF27" s="24" t="str">
-        <f t="shared" ca="1" si="34"/>
+        <f t="shared" ca="1" si="35"/>
         <v/>
       </c>
       <c r="BG27" s="24" t="str">
-        <f t="shared" ca="1" si="34"/>
+        <f t="shared" ca="1" si="35"/>
         <v/>
       </c>
       <c r="BH27" s="24" t="str">
-        <f t="shared" ca="1" si="34"/>
+        <f t="shared" ca="1" si="35"/>
         <v/>
       </c>
       <c r="BI27" s="24" t="str">
-        <f t="shared" ca="1" si="34"/>
+        <f t="shared" ca="1" si="35"/>
         <v/>
       </c>
       <c r="BJ27" s="24">
-        <f t="shared" ca="1" si="34"/>
+        <f t="shared" ca="1" si="35"/>
         <v>2</v>
       </c>
       <c r="BK27" s="24">
-        <f t="shared" ca="1" si="34"/>
+        <f t="shared" ca="1" si="35"/>
         <v>2</v>
       </c>
       <c r="BL27" s="24">
-        <f t="shared" ca="1" si="34"/>
+        <f t="shared" ca="1" si="35"/>
         <v>2</v>
       </c>
     </row>
@@ -9008,7 +9087,7 @@
         <v>0.7</v>
       </c>
       <c r="F28" s="56">
-        <f>F23+22</f>
+        <f t="shared" si="29"/>
         <v>46168</v>
       </c>
       <c r="G28" s="57">
@@ -9016,227 +9095,227 @@
       </c>
       <c r="H28" s="54"/>
       <c r="I28" s="24" t="str">
-        <f t="shared" ref="I28:AN28" ca="1" si="35">IF(AND($C26="Objectif",I$7&gt;=$F26,I$7&lt;=$F26+$G26-1),2,IF(AND($C26="Jalon",I$7&gt;=$F26,I$7&lt;=$F26+$G26-1),1,""))</f>
+        <f t="shared" ref="I28:AN28" ca="1" si="36">IF(AND($C26="Objectif",I$7&gt;=$F26,I$7&lt;=$F26+$G26-1),2,IF(AND($C26="Jalon",I$7&gt;=$F26,I$7&lt;=$F26+$G26-1),1,""))</f>
         <v/>
       </c>
       <c r="J28" s="24" t="str">
-        <f t="shared" ca="1" si="35"/>
+        <f t="shared" ca="1" si="36"/>
         <v/>
       </c>
       <c r="K28" s="24" t="str">
-        <f t="shared" ca="1" si="35"/>
+        <f t="shared" ca="1" si="36"/>
         <v/>
       </c>
       <c r="L28" s="24" t="str">
-        <f t="shared" ca="1" si="35"/>
+        <f t="shared" ca="1" si="36"/>
         <v/>
       </c>
       <c r="M28" s="24" t="str">
-        <f t="shared" ca="1" si="35"/>
+        <f t="shared" ca="1" si="36"/>
         <v/>
       </c>
       <c r="N28" s="24" t="str">
-        <f t="shared" ca="1" si="35"/>
+        <f t="shared" ca="1" si="36"/>
         <v/>
       </c>
       <c r="O28" s="24" t="str">
-        <f t="shared" ca="1" si="35"/>
+        <f t="shared" ca="1" si="36"/>
         <v/>
       </c>
       <c r="P28" s="24" t="str">
-        <f t="shared" ca="1" si="35"/>
+        <f t="shared" ca="1" si="36"/>
         <v/>
       </c>
       <c r="Q28" s="24" t="str">
-        <f t="shared" ca="1" si="35"/>
+        <f t="shared" ca="1" si="36"/>
         <v/>
       </c>
       <c r="R28" s="24" t="str">
-        <f t="shared" ca="1" si="35"/>
+        <f t="shared" ca="1" si="36"/>
         <v/>
       </c>
       <c r="S28" s="24" t="str">
-        <f t="shared" ca="1" si="35"/>
+        <f t="shared" ca="1" si="36"/>
         <v/>
       </c>
       <c r="T28" s="24" t="str">
-        <f t="shared" ca="1" si="35"/>
+        <f t="shared" ca="1" si="36"/>
         <v/>
       </c>
       <c r="U28" s="24" t="str">
-        <f t="shared" ca="1" si="35"/>
+        <f t="shared" ca="1" si="36"/>
         <v/>
       </c>
       <c r="V28" s="24" t="str">
-        <f t="shared" ca="1" si="35"/>
+        <f t="shared" ca="1" si="36"/>
         <v/>
       </c>
       <c r="W28" s="24" t="str">
-        <f t="shared" ca="1" si="35"/>
+        <f t="shared" ca="1" si="36"/>
         <v/>
       </c>
       <c r="X28" s="24" t="str">
-        <f t="shared" ca="1" si="35"/>
+        <f t="shared" ca="1" si="36"/>
         <v/>
       </c>
       <c r="Y28" s="24" t="str">
-        <f t="shared" ca="1" si="35"/>
+        <f t="shared" ca="1" si="36"/>
         <v/>
       </c>
       <c r="Z28" s="24" t="str">
-        <f t="shared" ca="1" si="35"/>
+        <f t="shared" ca="1" si="36"/>
         <v/>
       </c>
       <c r="AA28" s="24" t="str">
-        <f t="shared" ca="1" si="35"/>
+        <f t="shared" ca="1" si="36"/>
         <v/>
       </c>
       <c r="AB28" s="24" t="str">
-        <f t="shared" ca="1" si="35"/>
+        <f t="shared" ca="1" si="36"/>
         <v/>
       </c>
       <c r="AC28" s="24" t="str">
-        <f t="shared" ca="1" si="35"/>
+        <f t="shared" ca="1" si="36"/>
         <v/>
       </c>
       <c r="AD28" s="24" t="str">
-        <f t="shared" ca="1" si="35"/>
+        <f t="shared" ca="1" si="36"/>
         <v/>
       </c>
       <c r="AE28" s="24" t="str">
-        <f t="shared" ca="1" si="35"/>
+        <f t="shared" ca="1" si="36"/>
         <v/>
       </c>
       <c r="AF28" s="24" t="str">
-        <f t="shared" ca="1" si="35"/>
+        <f t="shared" ca="1" si="36"/>
         <v/>
       </c>
       <c r="AG28" s="24" t="str">
-        <f t="shared" ca="1" si="35"/>
+        <f t="shared" ca="1" si="36"/>
         <v/>
       </c>
       <c r="AH28" s="24" t="str">
-        <f t="shared" ca="1" si="35"/>
+        <f t="shared" ca="1" si="36"/>
         <v/>
       </c>
       <c r="AI28" s="24" t="str">
-        <f t="shared" ca="1" si="35"/>
+        <f t="shared" ca="1" si="36"/>
         <v/>
       </c>
       <c r="AJ28" s="24" t="str">
-        <f t="shared" ca="1" si="35"/>
+        <f t="shared" ca="1" si="36"/>
         <v/>
       </c>
       <c r="AK28" s="24" t="str">
-        <f t="shared" ca="1" si="35"/>
+        <f t="shared" ca="1" si="36"/>
         <v/>
       </c>
       <c r="AL28" s="24" t="str">
-        <f t="shared" ca="1" si="35"/>
+        <f t="shared" ca="1" si="36"/>
         <v/>
       </c>
       <c r="AM28" s="24" t="str">
-        <f t="shared" ca="1" si="35"/>
+        <f t="shared" ca="1" si="36"/>
         <v/>
       </c>
       <c r="AN28" s="24" t="str">
-        <f t="shared" ca="1" si="35"/>
+        <f t="shared" ca="1" si="36"/>
         <v/>
       </c>
       <c r="AO28" s="24" t="str">
-        <f t="shared" ref="AO28:BL28" ca="1" si="36">IF(AND($C26="Objectif",AO$7&gt;=$F26,AO$7&lt;=$F26+$G26-1),2,IF(AND($C26="Jalon",AO$7&gt;=$F26,AO$7&lt;=$F26+$G26-1),1,""))</f>
+        <f t="shared" ref="AO28:BL28" ca="1" si="37">IF(AND($C26="Objectif",AO$7&gt;=$F26,AO$7&lt;=$F26+$G26-1),2,IF(AND($C26="Jalon",AO$7&gt;=$F26,AO$7&lt;=$F26+$G26-1),1,""))</f>
         <v/>
       </c>
       <c r="AP28" s="24" t="str">
-        <f t="shared" ca="1" si="36"/>
+        <f t="shared" ca="1" si="37"/>
         <v/>
       </c>
       <c r="AQ28" s="24" t="str">
-        <f t="shared" ca="1" si="36"/>
+        <f t="shared" ca="1" si="37"/>
         <v/>
       </c>
       <c r="AR28" s="24" t="str">
-        <f t="shared" ca="1" si="36"/>
+        <f t="shared" ca="1" si="37"/>
         <v/>
       </c>
       <c r="AS28" s="24" t="str">
-        <f t="shared" ca="1" si="36"/>
+        <f t="shared" ca="1" si="37"/>
         <v/>
       </c>
       <c r="AT28" s="24" t="str">
-        <f t="shared" ca="1" si="36"/>
+        <f t="shared" ca="1" si="37"/>
         <v/>
       </c>
       <c r="AU28" s="24" t="str">
-        <f t="shared" ca="1" si="36"/>
+        <f t="shared" ca="1" si="37"/>
         <v/>
       </c>
       <c r="AV28" s="24" t="str">
-        <f t="shared" ca="1" si="36"/>
+        <f t="shared" ca="1" si="37"/>
         <v/>
       </c>
       <c r="AW28" s="24" t="str">
-        <f t="shared" ca="1" si="36"/>
+        <f t="shared" ca="1" si="37"/>
         <v/>
       </c>
       <c r="AX28" s="24" t="str">
-        <f t="shared" ca="1" si="36"/>
+        <f t="shared" ca="1" si="37"/>
         <v/>
       </c>
       <c r="AY28" s="24" t="str">
-        <f t="shared" ca="1" si="36"/>
+        <f t="shared" ca="1" si="37"/>
         <v/>
       </c>
       <c r="AZ28" s="24" t="str">
-        <f t="shared" ca="1" si="36"/>
+        <f t="shared" ca="1" si="37"/>
         <v/>
       </c>
       <c r="BA28" s="24" t="str">
-        <f t="shared" ca="1" si="36"/>
+        <f t="shared" ca="1" si="37"/>
         <v/>
       </c>
       <c r="BB28" s="24" t="str">
-        <f t="shared" ca="1" si="36"/>
+        <f t="shared" ca="1" si="37"/>
         <v/>
       </c>
       <c r="BC28" s="24" t="str">
-        <f t="shared" ca="1" si="36"/>
+        <f t="shared" ca="1" si="37"/>
         <v/>
       </c>
       <c r="BD28" s="24" t="str">
-        <f t="shared" ca="1" si="36"/>
+        <f t="shared" ca="1" si="37"/>
         <v/>
       </c>
       <c r="BE28" s="24" t="str">
-        <f t="shared" ca="1" si="36"/>
+        <f t="shared" ca="1" si="37"/>
         <v/>
       </c>
       <c r="BF28" s="24" t="str">
-        <f t="shared" ca="1" si="36"/>
+        <f t="shared" ca="1" si="37"/>
         <v/>
       </c>
       <c r="BG28" s="24" t="str">
-        <f t="shared" ca="1" si="36"/>
+        <f t="shared" ca="1" si="37"/>
         <v/>
       </c>
       <c r="BH28" s="24" t="str">
-        <f t="shared" ca="1" si="36"/>
+        <f t="shared" ca="1" si="37"/>
         <v/>
       </c>
       <c r="BI28" s="24" t="str">
-        <f t="shared" ca="1" si="36"/>
+        <f t="shared" ca="1" si="37"/>
         <v/>
       </c>
       <c r="BJ28" s="24" t="str">
-        <f t="shared" ca="1" si="36"/>
+        <f t="shared" ca="1" si="37"/>
         <v/>
       </c>
       <c r="BK28" s="24" t="str">
-        <f t="shared" ca="1" si="36"/>
+        <f t="shared" ca="1" si="37"/>
         <v/>
       </c>
       <c r="BL28" s="24" t="str">
-        <f t="shared" ca="1" si="36"/>
+        <f t="shared" ca="1" si="37"/>
         <v/>
       </c>
     </row>
@@ -9255,7 +9334,7 @@
         <v>0.8</v>
       </c>
       <c r="F29" s="56">
-        <f>F24+22</f>
+        <f t="shared" si="29"/>
         <v>46183</v>
       </c>
       <c r="G29" s="57">
@@ -9263,227 +9342,227 @@
       </c>
       <c r="H29" s="54"/>
       <c r="I29" s="24" t="str">
-        <f t="shared" ref="I29:AN29" ca="1" si="37">IF(AND($C27="Objectif",I$7&gt;=$F27,I$7&lt;=$F27+$G27-1),2,IF(AND($C27="Jalon",I$7&gt;=$F27,I$7&lt;=$F27+$G27-1),1,""))</f>
+        <f t="shared" ref="I29:AN29" ca="1" si="38">IF(AND($C27="Objectif",I$7&gt;=$F27,I$7&lt;=$F27+$G27-1),2,IF(AND($C27="Jalon",I$7&gt;=$F27,I$7&lt;=$F27+$G27-1),1,""))</f>
         <v/>
       </c>
       <c r="J29" s="24" t="str">
-        <f t="shared" ca="1" si="37"/>
+        <f t="shared" ca="1" si="38"/>
         <v/>
       </c>
       <c r="K29" s="24" t="str">
-        <f t="shared" ca="1" si="37"/>
+        <f t="shared" ca="1" si="38"/>
         <v/>
       </c>
       <c r="L29" s="24" t="str">
-        <f t="shared" ca="1" si="37"/>
+        <f t="shared" ca="1" si="38"/>
         <v/>
       </c>
       <c r="M29" s="24" t="str">
-        <f t="shared" ca="1" si="37"/>
+        <f t="shared" ca="1" si="38"/>
         <v/>
       </c>
       <c r="N29" s="24" t="str">
-        <f t="shared" ca="1" si="37"/>
+        <f t="shared" ca="1" si="38"/>
         <v/>
       </c>
       <c r="O29" s="24" t="str">
-        <f t="shared" ca="1" si="37"/>
+        <f t="shared" ca="1" si="38"/>
         <v/>
       </c>
       <c r="P29" s="24" t="str">
-        <f t="shared" ca="1" si="37"/>
+        <f t="shared" ca="1" si="38"/>
         <v/>
       </c>
       <c r="Q29" s="24" t="str">
-        <f t="shared" ca="1" si="37"/>
+        <f t="shared" ca="1" si="38"/>
         <v/>
       </c>
       <c r="R29" s="24" t="str">
-        <f t="shared" ca="1" si="37"/>
+        <f t="shared" ca="1" si="38"/>
         <v/>
       </c>
       <c r="S29" s="24" t="str">
-        <f t="shared" ca="1" si="37"/>
+        <f t="shared" ca="1" si="38"/>
         <v/>
       </c>
       <c r="T29" s="24" t="str">
-        <f t="shared" ca="1" si="37"/>
+        <f t="shared" ca="1" si="38"/>
         <v/>
       </c>
       <c r="U29" s="24" t="str">
-        <f t="shared" ca="1" si="37"/>
+        <f t="shared" ca="1" si="38"/>
         <v/>
       </c>
       <c r="V29" s="24" t="str">
-        <f t="shared" ca="1" si="37"/>
+        <f t="shared" ca="1" si="38"/>
         <v/>
       </c>
       <c r="W29" s="24" t="str">
-        <f t="shared" ca="1" si="37"/>
+        <f t="shared" ca="1" si="38"/>
         <v/>
       </c>
       <c r="X29" s="24" t="str">
-        <f t="shared" ca="1" si="37"/>
+        <f t="shared" ca="1" si="38"/>
         <v/>
       </c>
       <c r="Y29" s="24" t="str">
-        <f t="shared" ca="1" si="37"/>
+        <f t="shared" ca="1" si="38"/>
         <v/>
       </c>
       <c r="Z29" s="24" t="str">
-        <f t="shared" ca="1" si="37"/>
+        <f t="shared" ca="1" si="38"/>
         <v/>
       </c>
       <c r="AA29" s="24" t="str">
-        <f t="shared" ca="1" si="37"/>
+        <f t="shared" ca="1" si="38"/>
         <v/>
       </c>
       <c r="AB29" s="24" t="str">
-        <f t="shared" ca="1" si="37"/>
+        <f t="shared" ca="1" si="38"/>
         <v/>
       </c>
       <c r="AC29" s="24" t="str">
-        <f t="shared" ca="1" si="37"/>
+        <f t="shared" ca="1" si="38"/>
         <v/>
       </c>
       <c r="AD29" s="24" t="str">
-        <f t="shared" ca="1" si="37"/>
+        <f t="shared" ca="1" si="38"/>
         <v/>
       </c>
       <c r="AE29" s="24" t="str">
-        <f t="shared" ca="1" si="37"/>
+        <f t="shared" ca="1" si="38"/>
         <v/>
       </c>
       <c r="AF29" s="24" t="str">
-        <f t="shared" ca="1" si="37"/>
+        <f t="shared" ca="1" si="38"/>
         <v/>
       </c>
       <c r="AG29" s="24" t="str">
-        <f t="shared" ca="1" si="37"/>
+        <f t="shared" ca="1" si="38"/>
         <v/>
       </c>
       <c r="AH29" s="24" t="str">
-        <f t="shared" ca="1" si="37"/>
+        <f t="shared" ca="1" si="38"/>
         <v/>
       </c>
       <c r="AI29" s="24" t="str">
-        <f t="shared" ca="1" si="37"/>
+        <f t="shared" ca="1" si="38"/>
         <v/>
       </c>
       <c r="AJ29" s="24" t="str">
-        <f t="shared" ca="1" si="37"/>
+        <f t="shared" ca="1" si="38"/>
         <v/>
       </c>
       <c r="AK29" s="24" t="str">
-        <f t="shared" ca="1" si="37"/>
+        <f t="shared" ca="1" si="38"/>
         <v/>
       </c>
       <c r="AL29" s="24" t="str">
-        <f t="shared" ca="1" si="37"/>
+        <f t="shared" ca="1" si="38"/>
         <v/>
       </c>
       <c r="AM29" s="24" t="str">
-        <f t="shared" ca="1" si="37"/>
+        <f t="shared" ca="1" si="38"/>
         <v/>
       </c>
       <c r="AN29" s="24" t="str">
-        <f t="shared" ca="1" si="37"/>
+        <f t="shared" ca="1" si="38"/>
         <v/>
       </c>
       <c r="AO29" s="24" t="str">
-        <f t="shared" ref="AO29:BL29" ca="1" si="38">IF(AND($C27="Objectif",AO$7&gt;=$F27,AO$7&lt;=$F27+$G27-1),2,IF(AND($C27="Jalon",AO$7&gt;=$F27,AO$7&lt;=$F27+$G27-1),1,""))</f>
+        <f t="shared" ref="AO29:BL29" ca="1" si="39">IF(AND($C27="Objectif",AO$7&gt;=$F27,AO$7&lt;=$F27+$G27-1),2,IF(AND($C27="Jalon",AO$7&gt;=$F27,AO$7&lt;=$F27+$G27-1),1,""))</f>
         <v/>
       </c>
       <c r="AP29" s="24" t="str">
-        <f t="shared" ca="1" si="38"/>
+        <f t="shared" ca="1" si="39"/>
         <v/>
       </c>
       <c r="AQ29" s="24" t="str">
-        <f t="shared" ca="1" si="38"/>
+        <f t="shared" ca="1" si="39"/>
         <v/>
       </c>
       <c r="AR29" s="24" t="str">
-        <f t="shared" ca="1" si="38"/>
+        <f t="shared" ca="1" si="39"/>
         <v/>
       </c>
       <c r="AS29" s="24">
-        <f t="shared" ca="1" si="38"/>
+        <f t="shared" ca="1" si="39"/>
         <v>1</v>
       </c>
       <c r="AT29" s="24" t="str">
-        <f t="shared" ca="1" si="38"/>
+        <f t="shared" ca="1" si="39"/>
         <v/>
       </c>
       <c r="AU29" s="24" t="str">
-        <f t="shared" ca="1" si="38"/>
+        <f t="shared" ca="1" si="39"/>
         <v/>
       </c>
       <c r="AV29" s="24" t="str">
-        <f t="shared" ca="1" si="38"/>
+        <f t="shared" ca="1" si="39"/>
         <v/>
       </c>
       <c r="AW29" s="24" t="str">
-        <f t="shared" ca="1" si="38"/>
+        <f t="shared" ca="1" si="39"/>
         <v/>
       </c>
       <c r="AX29" s="24" t="str">
-        <f t="shared" ca="1" si="38"/>
+        <f t="shared" ca="1" si="39"/>
         <v/>
       </c>
       <c r="AY29" s="24" t="str">
-        <f t="shared" ca="1" si="38"/>
+        <f t="shared" ca="1" si="39"/>
         <v/>
       </c>
       <c r="AZ29" s="24" t="str">
-        <f t="shared" ca="1" si="38"/>
+        <f t="shared" ca="1" si="39"/>
         <v/>
       </c>
       <c r="BA29" s="24" t="str">
-        <f t="shared" ca="1" si="38"/>
+        <f t="shared" ca="1" si="39"/>
         <v/>
       </c>
       <c r="BB29" s="24" t="str">
-        <f t="shared" ca="1" si="38"/>
+        <f t="shared" ca="1" si="39"/>
         <v/>
       </c>
       <c r="BC29" s="24" t="str">
-        <f t="shared" ca="1" si="38"/>
+        <f t="shared" ca="1" si="39"/>
         <v/>
       </c>
       <c r="BD29" s="24" t="str">
-        <f t="shared" ca="1" si="38"/>
+        <f t="shared" ca="1" si="39"/>
         <v/>
       </c>
       <c r="BE29" s="24" t="str">
-        <f t="shared" ca="1" si="38"/>
+        <f t="shared" ca="1" si="39"/>
         <v/>
       </c>
       <c r="BF29" s="24" t="str">
-        <f t="shared" ca="1" si="38"/>
+        <f t="shared" ca="1" si="39"/>
         <v/>
       </c>
       <c r="BG29" s="24" t="str">
-        <f t="shared" ca="1" si="38"/>
+        <f t="shared" ca="1" si="39"/>
         <v/>
       </c>
       <c r="BH29" s="24" t="str">
-        <f t="shared" ca="1" si="38"/>
+        <f t="shared" ca="1" si="39"/>
         <v/>
       </c>
       <c r="BI29" s="24" t="str">
-        <f t="shared" ca="1" si="38"/>
+        <f t="shared" ca="1" si="39"/>
         <v/>
       </c>
       <c r="BJ29" s="24" t="str">
-        <f t="shared" ca="1" si="38"/>
+        <f t="shared" ca="1" si="39"/>
         <v/>
       </c>
       <c r="BK29" s="24" t="str">
-        <f t="shared" ca="1" si="38"/>
+        <f t="shared" ca="1" si="39"/>
         <v/>
       </c>
       <c r="BL29" s="24" t="str">
-        <f t="shared" ca="1" si="38"/>
+        <f t="shared" ca="1" si="39"/>
         <v/>
       </c>
     </row>
@@ -9502,7 +9581,7 @@
         <v>0.8</v>
       </c>
       <c r="F30" s="56">
-        <f>F25+22</f>
+        <f t="shared" si="29"/>
         <v>46204</v>
       </c>
       <c r="G30" s="57">
@@ -9510,233 +9589,233 @@
       </c>
       <c r="H30" s="54"/>
       <c r="I30" s="24" t="str">
-        <f t="shared" ref="I30:AN30" ca="1" si="39">IF(AND($C28="Objectif",I$7&gt;=$F28,I$7&lt;=$F28+$G28-1),2,IF(AND($C28="Jalon",I$7&gt;=$F28,I$7&lt;=$F28+$G28-1),1,""))</f>
+        <f t="shared" ref="I30:AN30" ca="1" si="40">IF(AND($C28="Objectif",I$7&gt;=$F28,I$7&lt;=$F28+$G28-1),2,IF(AND($C28="Jalon",I$7&gt;=$F28,I$7&lt;=$F28+$G28-1),1,""))</f>
         <v/>
       </c>
       <c r="J30" s="24" t="str">
-        <f t="shared" ca="1" si="39"/>
+        <f t="shared" ca="1" si="40"/>
         <v/>
       </c>
       <c r="K30" s="24" t="str">
-        <f t="shared" ca="1" si="39"/>
+        <f t="shared" ca="1" si="40"/>
         <v/>
       </c>
       <c r="L30" s="24" t="str">
-        <f t="shared" ca="1" si="39"/>
+        <f t="shared" ca="1" si="40"/>
         <v/>
       </c>
       <c r="M30" s="24" t="str">
-        <f t="shared" ca="1" si="39"/>
+        <f t="shared" ca="1" si="40"/>
         <v/>
       </c>
       <c r="N30" s="24" t="str">
-        <f t="shared" ca="1" si="39"/>
+        <f t="shared" ca="1" si="40"/>
         <v/>
       </c>
       <c r="O30" s="24" t="str">
-        <f t="shared" ca="1" si="39"/>
+        <f t="shared" ca="1" si="40"/>
         <v/>
       </c>
       <c r="P30" s="24" t="str">
-        <f t="shared" ca="1" si="39"/>
+        <f t="shared" ca="1" si="40"/>
         <v/>
       </c>
       <c r="Q30" s="24" t="str">
-        <f t="shared" ca="1" si="39"/>
+        <f t="shared" ca="1" si="40"/>
         <v/>
       </c>
       <c r="R30" s="24" t="str">
-        <f t="shared" ca="1" si="39"/>
+        <f t="shared" ca="1" si="40"/>
         <v/>
       </c>
       <c r="S30" s="24" t="str">
-        <f t="shared" ca="1" si="39"/>
+        <f t="shared" ca="1" si="40"/>
         <v/>
       </c>
       <c r="T30" s="24" t="str">
-        <f t="shared" ca="1" si="39"/>
+        <f t="shared" ca="1" si="40"/>
         <v/>
       </c>
       <c r="U30" s="24" t="str">
-        <f t="shared" ca="1" si="39"/>
+        <f t="shared" ca="1" si="40"/>
         <v/>
       </c>
       <c r="V30" s="24" t="str">
-        <f t="shared" ca="1" si="39"/>
+        <f t="shared" ca="1" si="40"/>
         <v/>
       </c>
       <c r="W30" s="24" t="str">
-        <f t="shared" ca="1" si="39"/>
+        <f t="shared" ca="1" si="40"/>
         <v/>
       </c>
       <c r="X30" s="24" t="str">
-        <f t="shared" ca="1" si="39"/>
+        <f t="shared" ca="1" si="40"/>
         <v/>
       </c>
       <c r="Y30" s="24" t="str">
-        <f t="shared" ca="1" si="39"/>
+        <f t="shared" ca="1" si="40"/>
         <v/>
       </c>
       <c r="Z30" s="24" t="str">
-        <f t="shared" ca="1" si="39"/>
+        <f t="shared" ca="1" si="40"/>
         <v/>
       </c>
       <c r="AA30" s="24" t="str">
-        <f t="shared" ca="1" si="39"/>
+        <f t="shared" ca="1" si="40"/>
         <v/>
       </c>
       <c r="AB30" s="24" t="str">
-        <f t="shared" ca="1" si="39"/>
+        <f t="shared" ca="1" si="40"/>
         <v/>
       </c>
       <c r="AC30" s="24" t="str">
-        <f t="shared" ca="1" si="39"/>
+        <f t="shared" ca="1" si="40"/>
         <v/>
       </c>
       <c r="AD30" s="24" t="str">
-        <f t="shared" ca="1" si="39"/>
+        <f t="shared" ca="1" si="40"/>
         <v/>
       </c>
       <c r="AE30" s="24" t="str">
-        <f t="shared" ca="1" si="39"/>
+        <f t="shared" ca="1" si="40"/>
         <v/>
       </c>
       <c r="AF30" s="24" t="str">
-        <f t="shared" ca="1" si="39"/>
+        <f t="shared" ca="1" si="40"/>
         <v/>
       </c>
       <c r="AG30" s="24" t="str">
-        <f t="shared" ca="1" si="39"/>
+        <f t="shared" ca="1" si="40"/>
         <v/>
       </c>
       <c r="AH30" s="24" t="str">
-        <f t="shared" ca="1" si="39"/>
+        <f t="shared" ca="1" si="40"/>
         <v/>
       </c>
       <c r="AI30" s="24" t="str">
-        <f t="shared" ca="1" si="39"/>
+        <f t="shared" ca="1" si="40"/>
         <v/>
       </c>
       <c r="AJ30" s="24" t="str">
-        <f t="shared" ca="1" si="39"/>
+        <f t="shared" ca="1" si="40"/>
         <v/>
       </c>
       <c r="AK30" s="24" t="str">
-        <f t="shared" ca="1" si="39"/>
+        <f t="shared" ca="1" si="40"/>
         <v/>
       </c>
       <c r="AL30" s="24" t="str">
-        <f t="shared" ca="1" si="39"/>
+        <f t="shared" ca="1" si="40"/>
         <v/>
       </c>
       <c r="AM30" s="24" t="str">
-        <f t="shared" ca="1" si="39"/>
+        <f t="shared" ca="1" si="40"/>
         <v/>
       </c>
       <c r="AN30" s="24" t="str">
-        <f t="shared" ca="1" si="39"/>
+        <f t="shared" ca="1" si="40"/>
         <v/>
       </c>
       <c r="AO30" s="24" t="str">
-        <f t="shared" ref="AO30:BL30" ca="1" si="40">IF(AND($C28="Objectif",AO$7&gt;=$F28,AO$7&lt;=$F28+$G28-1),2,IF(AND($C28="Jalon",AO$7&gt;=$F28,AO$7&lt;=$F28+$G28-1),1,""))</f>
+        <f t="shared" ref="AO30:BL30" ca="1" si="41">IF(AND($C28="Objectif",AO$7&gt;=$F28,AO$7&lt;=$F28+$G28-1),2,IF(AND($C28="Jalon",AO$7&gt;=$F28,AO$7&lt;=$F28+$G28-1),1,""))</f>
         <v/>
       </c>
       <c r="AP30" s="24" t="str">
-        <f t="shared" ca="1" si="40"/>
+        <f t="shared" ca="1" si="41"/>
         <v/>
       </c>
       <c r="AQ30" s="24" t="str">
-        <f t="shared" ca="1" si="40"/>
+        <f t="shared" ca="1" si="41"/>
         <v/>
       </c>
       <c r="AR30" s="24" t="str">
-        <f t="shared" ca="1" si="40"/>
+        <f t="shared" ca="1" si="41"/>
         <v/>
       </c>
       <c r="AS30" s="24" t="str">
-        <f t="shared" ca="1" si="40"/>
+        <f t="shared" ca="1" si="41"/>
         <v/>
       </c>
       <c r="AT30" s="24" t="str">
-        <f t="shared" ca="1" si="40"/>
+        <f t="shared" ca="1" si="41"/>
         <v/>
       </c>
       <c r="AU30" s="24" t="str">
-        <f t="shared" ca="1" si="40"/>
+        <f t="shared" ca="1" si="41"/>
         <v/>
       </c>
       <c r="AV30" s="24">
-        <f t="shared" ca="1" si="40"/>
+        <f t="shared" ca="1" si="41"/>
         <v>1</v>
       </c>
       <c r="AW30" s="24">
-        <f t="shared" ca="1" si="40"/>
+        <f t="shared" ca="1" si="41"/>
         <v>1</v>
       </c>
       <c r="AX30" s="24">
-        <f t="shared" ca="1" si="40"/>
+        <f t="shared" ca="1" si="41"/>
         <v>1</v>
       </c>
       <c r="AY30" s="24">
-        <f t="shared" ca="1" si="40"/>
+        <f t="shared" ca="1" si="41"/>
         <v>1</v>
       </c>
       <c r="AZ30" s="24">
-        <f t="shared" ca="1" si="40"/>
+        <f t="shared" ca="1" si="41"/>
         <v>1</v>
       </c>
       <c r="BA30" s="24">
-        <f t="shared" ca="1" si="40"/>
+        <f t="shared" ca="1" si="41"/>
         <v>1</v>
       </c>
       <c r="BB30" s="24">
-        <f t="shared" ca="1" si="40"/>
+        <f t="shared" ca="1" si="41"/>
         <v>1</v>
       </c>
       <c r="BC30" s="24">
-        <f t="shared" ca="1" si="40"/>
+        <f t="shared" ca="1" si="41"/>
         <v>1</v>
       </c>
       <c r="BD30" s="24">
-        <f t="shared" ca="1" si="40"/>
+        <f t="shared" ca="1" si="41"/>
         <v>1</v>
       </c>
       <c r="BE30" s="24">
-        <f t="shared" ca="1" si="40"/>
+        <f t="shared" ca="1" si="41"/>
         <v>1</v>
       </c>
       <c r="BF30" s="24">
-        <f t="shared" ca="1" si="40"/>
+        <f t="shared" ca="1" si="41"/>
         <v>1</v>
       </c>
       <c r="BG30" s="24">
-        <f t="shared" ca="1" si="40"/>
+        <f t="shared" ca="1" si="41"/>
         <v>1</v>
       </c>
       <c r="BH30" s="24">
-        <f t="shared" ca="1" si="40"/>
+        <f t="shared" ca="1" si="41"/>
         <v>1</v>
       </c>
       <c r="BI30" s="24">
-        <f t="shared" ca="1" si="40"/>
+        <f t="shared" ca="1" si="41"/>
         <v>1</v>
       </c>
       <c r="BJ30" s="24">
-        <f t="shared" ca="1" si="40"/>
+        <f t="shared" ca="1" si="41"/>
         <v>1</v>
       </c>
       <c r="BK30" s="24" t="str">
-        <f t="shared" ca="1" si="40"/>
+        <f t="shared" ca="1" si="41"/>
         <v/>
       </c>
       <c r="BL30" s="24" t="str">
-        <f t="shared" ca="1" si="40"/>
+        <f t="shared" ca="1" si="41"/>
         <v/>
       </c>
     </row>
     <row r="31" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="9"/>
-      <c r="B31" s="149" t="s">
+      <c r="B31" s="129" t="s">
         <v>76</v>
       </c>
       <c r="C31" s="54" t="s">
@@ -9749,7 +9828,7 @@
         <v>0.8</v>
       </c>
       <c r="F31" s="56">
-        <f>F26+22</f>
+        <f t="shared" si="29"/>
         <v>46205</v>
       </c>
       <c r="G31" s="57">
@@ -9757,227 +9836,227 @@
       </c>
       <c r="H31" s="54"/>
       <c r="I31" s="24" t="str">
-        <f t="shared" ref="I31:AN31" ca="1" si="41">IF(AND($C29="Objectif",I$7&gt;=$F29,I$7&lt;=$F29+$G29-1),2,IF(AND($C29="Jalon",I$7&gt;=$F29,I$7&lt;=$F29+$G29-1),1,""))</f>
+        <f t="shared" ref="I31:AN31" ca="1" si="42">IF(AND($C29="Objectif",I$7&gt;=$F29,I$7&lt;=$F29+$G29-1),2,IF(AND($C29="Jalon",I$7&gt;=$F29,I$7&lt;=$F29+$G29-1),1,""))</f>
         <v/>
       </c>
       <c r="J31" s="24" t="str">
-        <f t="shared" ca="1" si="41"/>
+        <f t="shared" ca="1" si="42"/>
         <v/>
       </c>
       <c r="K31" s="24" t="str">
-        <f t="shared" ca="1" si="41"/>
+        <f t="shared" ca="1" si="42"/>
         <v/>
       </c>
       <c r="L31" s="24" t="str">
-        <f t="shared" ca="1" si="41"/>
+        <f t="shared" ca="1" si="42"/>
         <v/>
       </c>
       <c r="M31" s="24" t="str">
-        <f t="shared" ca="1" si="41"/>
+        <f t="shared" ca="1" si="42"/>
         <v/>
       </c>
       <c r="N31" s="24" t="str">
-        <f t="shared" ca="1" si="41"/>
+        <f t="shared" ca="1" si="42"/>
         <v/>
       </c>
       <c r="O31" s="24" t="str">
-        <f t="shared" ca="1" si="41"/>
+        <f t="shared" ca="1" si="42"/>
         <v/>
       </c>
       <c r="P31" s="24" t="str">
-        <f t="shared" ca="1" si="41"/>
+        <f t="shared" ca="1" si="42"/>
         <v/>
       </c>
       <c r="Q31" s="24" t="str">
-        <f t="shared" ca="1" si="41"/>
+        <f t="shared" ca="1" si="42"/>
         <v/>
       </c>
       <c r="R31" s="24" t="str">
-        <f t="shared" ca="1" si="41"/>
+        <f t="shared" ca="1" si="42"/>
         <v/>
       </c>
       <c r="S31" s="24" t="str">
-        <f t="shared" ca="1" si="41"/>
+        <f t="shared" ca="1" si="42"/>
         <v/>
       </c>
       <c r="T31" s="24" t="str">
-        <f t="shared" ca="1" si="41"/>
+        <f t="shared" ca="1" si="42"/>
         <v/>
       </c>
       <c r="U31" s="24" t="str">
-        <f t="shared" ca="1" si="41"/>
+        <f t="shared" ca="1" si="42"/>
         <v/>
       </c>
       <c r="V31" s="24" t="str">
-        <f t="shared" ca="1" si="41"/>
+        <f t="shared" ca="1" si="42"/>
         <v/>
       </c>
       <c r="W31" s="24" t="str">
-        <f t="shared" ca="1" si="41"/>
+        <f t="shared" ca="1" si="42"/>
         <v/>
       </c>
       <c r="X31" s="24" t="str">
-        <f t="shared" ca="1" si="41"/>
+        <f t="shared" ca="1" si="42"/>
         <v/>
       </c>
       <c r="Y31" s="24" t="str">
-        <f t="shared" ca="1" si="41"/>
+        <f t="shared" ca="1" si="42"/>
         <v/>
       </c>
       <c r="Z31" s="24" t="str">
-        <f t="shared" ca="1" si="41"/>
+        <f t="shared" ca="1" si="42"/>
         <v/>
       </c>
       <c r="AA31" s="24" t="str">
-        <f t="shared" ca="1" si="41"/>
+        <f t="shared" ca="1" si="42"/>
         <v/>
       </c>
       <c r="AB31" s="24" t="str">
-        <f t="shared" ca="1" si="41"/>
+        <f t="shared" ca="1" si="42"/>
         <v/>
       </c>
       <c r="AC31" s="24" t="str">
-        <f t="shared" ca="1" si="41"/>
+        <f t="shared" ca="1" si="42"/>
         <v/>
       </c>
       <c r="AD31" s="24" t="str">
-        <f t="shared" ca="1" si="41"/>
+        <f t="shared" ca="1" si="42"/>
         <v/>
       </c>
       <c r="AE31" s="24" t="str">
-        <f t="shared" ca="1" si="41"/>
+        <f t="shared" ca="1" si="42"/>
         <v/>
       </c>
       <c r="AF31" s="24" t="str">
-        <f t="shared" ca="1" si="41"/>
+        <f t="shared" ca="1" si="42"/>
         <v/>
       </c>
       <c r="AG31" s="24" t="str">
-        <f t="shared" ca="1" si="41"/>
+        <f t="shared" ca="1" si="42"/>
         <v/>
       </c>
       <c r="AH31" s="24" t="str">
-        <f t="shared" ca="1" si="41"/>
+        <f t="shared" ca="1" si="42"/>
         <v/>
       </c>
       <c r="AI31" s="24" t="str">
-        <f t="shared" ca="1" si="41"/>
+        <f t="shared" ca="1" si="42"/>
         <v/>
       </c>
       <c r="AJ31" s="24" t="str">
-        <f t="shared" ca="1" si="41"/>
+        <f t="shared" ca="1" si="42"/>
         <v/>
       </c>
       <c r="AK31" s="24" t="str">
-        <f t="shared" ca="1" si="41"/>
+        <f t="shared" ca="1" si="42"/>
         <v/>
       </c>
       <c r="AL31" s="24" t="str">
-        <f t="shared" ca="1" si="41"/>
+        <f t="shared" ca="1" si="42"/>
         <v/>
       </c>
       <c r="AM31" s="24" t="str">
-        <f t="shared" ca="1" si="41"/>
+        <f t="shared" ca="1" si="42"/>
         <v/>
       </c>
       <c r="AN31" s="24" t="str">
-        <f t="shared" ca="1" si="41"/>
+        <f t="shared" ca="1" si="42"/>
         <v/>
       </c>
       <c r="AO31" s="24" t="str">
-        <f t="shared" ref="AO31:BL31" ca="1" si="42">IF(AND($C29="Objectif",AO$7&gt;=$F29,AO$7&lt;=$F29+$G29-1),2,IF(AND($C29="Jalon",AO$7&gt;=$F29,AO$7&lt;=$F29+$G29-1),1,""))</f>
+        <f t="shared" ref="AO31:BL31" ca="1" si="43">IF(AND($C29="Objectif",AO$7&gt;=$F29,AO$7&lt;=$F29+$G29-1),2,IF(AND($C29="Jalon",AO$7&gt;=$F29,AO$7&lt;=$F29+$G29-1),1,""))</f>
         <v/>
       </c>
       <c r="AP31" s="24" t="str">
-        <f t="shared" ca="1" si="42"/>
+        <f t="shared" ca="1" si="43"/>
         <v/>
       </c>
       <c r="AQ31" s="24" t="str">
-        <f t="shared" ca="1" si="42"/>
+        <f t="shared" ca="1" si="43"/>
         <v/>
       </c>
       <c r="AR31" s="24" t="str">
-        <f t="shared" ca="1" si="42"/>
+        <f t="shared" ca="1" si="43"/>
         <v/>
       </c>
       <c r="AS31" s="24" t="str">
-        <f t="shared" ca="1" si="42"/>
+        <f t="shared" ca="1" si="43"/>
         <v/>
       </c>
       <c r="AT31" s="24" t="str">
-        <f t="shared" ca="1" si="42"/>
+        <f t="shared" ca="1" si="43"/>
         <v/>
       </c>
       <c r="AU31" s="24" t="str">
-        <f t="shared" ca="1" si="42"/>
+        <f t="shared" ca="1" si="43"/>
         <v/>
       </c>
       <c r="AV31" s="24" t="str">
-        <f t="shared" ca="1" si="42"/>
+        <f t="shared" ca="1" si="43"/>
         <v/>
       </c>
       <c r="AW31" s="24" t="str">
-        <f t="shared" ca="1" si="42"/>
+        <f t="shared" ca="1" si="43"/>
         <v/>
       </c>
       <c r="AX31" s="24" t="str">
-        <f t="shared" ca="1" si="42"/>
+        <f t="shared" ca="1" si="43"/>
         <v/>
       </c>
       <c r="AY31" s="24" t="str">
-        <f t="shared" ca="1" si="42"/>
+        <f t="shared" ca="1" si="43"/>
         <v/>
       </c>
       <c r="AZ31" s="24" t="str">
-        <f t="shared" ca="1" si="42"/>
+        <f t="shared" ca="1" si="43"/>
         <v/>
       </c>
       <c r="BA31" s="24" t="str">
-        <f t="shared" ca="1" si="42"/>
+        <f t="shared" ca="1" si="43"/>
         <v/>
       </c>
       <c r="BB31" s="24" t="str">
-        <f t="shared" ca="1" si="42"/>
+        <f t="shared" ca="1" si="43"/>
         <v/>
       </c>
       <c r="BC31" s="24" t="str">
-        <f t="shared" ca="1" si="42"/>
+        <f t="shared" ca="1" si="43"/>
         <v/>
       </c>
       <c r="BD31" s="24" t="str">
-        <f t="shared" ca="1" si="42"/>
+        <f t="shared" ca="1" si="43"/>
         <v/>
       </c>
       <c r="BE31" s="24" t="str">
-        <f t="shared" ca="1" si="42"/>
+        <f t="shared" ca="1" si="43"/>
         <v/>
       </c>
       <c r="BF31" s="24" t="str">
-        <f t="shared" ca="1" si="42"/>
+        <f t="shared" ca="1" si="43"/>
         <v/>
       </c>
       <c r="BG31" s="24" t="str">
-        <f t="shared" ca="1" si="42"/>
+        <f t="shared" ca="1" si="43"/>
         <v/>
       </c>
       <c r="BH31" s="24" t="str">
-        <f t="shared" ca="1" si="42"/>
+        <f t="shared" ca="1" si="43"/>
         <v/>
       </c>
       <c r="BI31" s="24" t="str">
-        <f t="shared" ca="1" si="42"/>
+        <f t="shared" ca="1" si="43"/>
         <v/>
       </c>
       <c r="BJ31" s="24" t="str">
-        <f t="shared" ca="1" si="42"/>
+        <f t="shared" ca="1" si="43"/>
         <v/>
       </c>
       <c r="BK31" s="24" t="str">
-        <f t="shared" ca="1" si="42"/>
+        <f t="shared" ca="1" si="43"/>
         <v/>
       </c>
       <c r="BL31" s="24" t="str">
-        <f t="shared" ca="1" si="42"/>
+        <f t="shared" ca="1" si="43"/>
         <v/>
       </c>
     </row>
@@ -9994,233 +10073,233 @@
       </c>
       <c r="E32" s="55"/>
       <c r="F32" s="56">
-        <f>F27+22</f>
+        <f t="shared" si="29"/>
         <v>46187</v>
       </c>
       <c r="G32" s="57"/>
       <c r="H32" s="54"/>
       <c r="I32" s="24" t="str">
-        <f t="shared" ref="I32:AN32" ca="1" si="43">IF(AND($C30="Objectif",I$7&gt;=$F30,I$7&lt;=$F30+$G30-1),2,IF(AND($C30="Jalon",I$7&gt;=$F30,I$7&lt;=$F30+$G30-1),1,""))</f>
+        <f t="shared" ref="I32:AN32" ca="1" si="44">IF(AND($C30="Objectif",I$7&gt;=$F30,I$7&lt;=$F30+$G30-1),2,IF(AND($C30="Jalon",I$7&gt;=$F30,I$7&lt;=$F30+$G30-1),1,""))</f>
         <v/>
       </c>
       <c r="J32" s="24" t="str">
-        <f t="shared" ca="1" si="43"/>
+        <f t="shared" ca="1" si="44"/>
         <v/>
       </c>
       <c r="K32" s="24" t="str">
-        <f t="shared" ca="1" si="43"/>
+        <f t="shared" ca="1" si="44"/>
         <v/>
       </c>
       <c r="L32" s="24" t="str">
-        <f t="shared" ca="1" si="43"/>
+        <f t="shared" ca="1" si="44"/>
         <v/>
       </c>
       <c r="M32" s="24" t="str">
-        <f t="shared" ca="1" si="43"/>
+        <f t="shared" ca="1" si="44"/>
         <v/>
       </c>
       <c r="N32" s="24" t="str">
-        <f t="shared" ca="1" si="43"/>
+        <f t="shared" ca="1" si="44"/>
         <v/>
       </c>
       <c r="O32" s="24" t="str">
-        <f t="shared" ca="1" si="43"/>
+        <f t="shared" ca="1" si="44"/>
         <v/>
       </c>
       <c r="P32" s="24" t="str">
-        <f t="shared" ca="1" si="43"/>
+        <f t="shared" ca="1" si="44"/>
         <v/>
       </c>
       <c r="Q32" s="24" t="str">
-        <f t="shared" ca="1" si="43"/>
+        <f t="shared" ca="1" si="44"/>
         <v/>
       </c>
       <c r="R32" s="24" t="str">
-        <f t="shared" ca="1" si="43"/>
+        <f t="shared" ca="1" si="44"/>
         <v/>
       </c>
       <c r="S32" s="24" t="str">
-        <f t="shared" ca="1" si="43"/>
+        <f t="shared" ca="1" si="44"/>
         <v/>
       </c>
       <c r="T32" s="24" t="str">
-        <f t="shared" ca="1" si="43"/>
+        <f t="shared" ca="1" si="44"/>
         <v/>
       </c>
       <c r="U32" s="24" t="str">
-        <f t="shared" ca="1" si="43"/>
+        <f t="shared" ca="1" si="44"/>
         <v/>
       </c>
       <c r="V32" s="24" t="str">
-        <f t="shared" ca="1" si="43"/>
+        <f t="shared" ca="1" si="44"/>
         <v/>
       </c>
       <c r="W32" s="24" t="str">
-        <f t="shared" ca="1" si="43"/>
+        <f t="shared" ca="1" si="44"/>
         <v/>
       </c>
       <c r="X32" s="24" t="str">
-        <f t="shared" ca="1" si="43"/>
+        <f t="shared" ca="1" si="44"/>
         <v/>
       </c>
       <c r="Y32" s="24" t="str">
-        <f t="shared" ca="1" si="43"/>
+        <f t="shared" ca="1" si="44"/>
         <v/>
       </c>
       <c r="Z32" s="24" t="str">
-        <f t="shared" ca="1" si="43"/>
+        <f t="shared" ca="1" si="44"/>
         <v/>
       </c>
       <c r="AA32" s="24" t="str">
-        <f t="shared" ca="1" si="43"/>
+        <f t="shared" ca="1" si="44"/>
         <v/>
       </c>
       <c r="AB32" s="24" t="str">
-        <f t="shared" ca="1" si="43"/>
+        <f t="shared" ca="1" si="44"/>
         <v/>
       </c>
       <c r="AC32" s="24" t="str">
-        <f t="shared" ca="1" si="43"/>
+        <f t="shared" ca="1" si="44"/>
         <v/>
       </c>
       <c r="AD32" s="24" t="str">
-        <f t="shared" ca="1" si="43"/>
+        <f t="shared" ca="1" si="44"/>
         <v/>
       </c>
       <c r="AE32" s="24" t="str">
-        <f t="shared" ca="1" si="43"/>
+        <f t="shared" ca="1" si="44"/>
         <v/>
       </c>
       <c r="AF32" s="24" t="str">
-        <f t="shared" ca="1" si="43"/>
+        <f t="shared" ca="1" si="44"/>
         <v/>
       </c>
       <c r="AG32" s="24" t="str">
-        <f t="shared" ca="1" si="43"/>
+        <f t="shared" ca="1" si="44"/>
         <v/>
       </c>
       <c r="AH32" s="24" t="str">
-        <f t="shared" ca="1" si="43"/>
+        <f t="shared" ca="1" si="44"/>
         <v/>
       </c>
       <c r="AI32" s="24" t="str">
-        <f t="shared" ca="1" si="43"/>
+        <f t="shared" ca="1" si="44"/>
         <v/>
       </c>
       <c r="AJ32" s="24" t="str">
-        <f t="shared" ca="1" si="43"/>
+        <f t="shared" ca="1" si="44"/>
         <v/>
       </c>
       <c r="AK32" s="24" t="str">
-        <f t="shared" ca="1" si="43"/>
+        <f t="shared" ca="1" si="44"/>
         <v/>
       </c>
       <c r="AL32" s="24" t="str">
-        <f t="shared" ca="1" si="43"/>
+        <f t="shared" ca="1" si="44"/>
         <v/>
       </c>
       <c r="AM32" s="24" t="str">
-        <f t="shared" ca="1" si="43"/>
+        <f t="shared" ca="1" si="44"/>
         <v/>
       </c>
       <c r="AN32" s="24" t="str">
-        <f t="shared" ca="1" si="43"/>
+        <f t="shared" ca="1" si="44"/>
         <v/>
       </c>
       <c r="AO32" s="24" t="str">
-        <f t="shared" ref="AO32:BL32" ca="1" si="44">IF(AND($C30="Objectif",AO$7&gt;=$F30,AO$7&lt;=$F30+$G30-1),2,IF(AND($C30="Jalon",AO$7&gt;=$F30,AO$7&lt;=$F30+$G30-1),1,""))</f>
+        <f t="shared" ref="AO32:BL32" ca="1" si="45">IF(AND($C30="Objectif",AO$7&gt;=$F30,AO$7&lt;=$F30+$G30-1),2,IF(AND($C30="Jalon",AO$7&gt;=$F30,AO$7&lt;=$F30+$G30-1),1,""))</f>
         <v/>
       </c>
       <c r="AP32" s="24" t="str">
-        <f t="shared" ca="1" si="44"/>
+        <f t="shared" ca="1" si="45"/>
         <v/>
       </c>
       <c r="AQ32" s="24" t="str">
-        <f t="shared" ca="1" si="44"/>
+        <f t="shared" ca="1" si="45"/>
         <v/>
       </c>
       <c r="AR32" s="24" t="str">
-        <f t="shared" ca="1" si="44"/>
+        <f t="shared" ca="1" si="45"/>
         <v/>
       </c>
       <c r="AS32" s="24" t="str">
-        <f t="shared" ca="1" si="44"/>
+        <f t="shared" ca="1" si="45"/>
         <v/>
       </c>
       <c r="AT32" s="24" t="str">
-        <f t="shared" ca="1" si="44"/>
+        <f t="shared" ca="1" si="45"/>
         <v/>
       </c>
       <c r="AU32" s="24" t="str">
-        <f t="shared" ca="1" si="44"/>
+        <f t="shared" ca="1" si="45"/>
         <v/>
       </c>
       <c r="AV32" s="24" t="str">
-        <f t="shared" ca="1" si="44"/>
+        <f t="shared" ca="1" si="45"/>
         <v/>
       </c>
       <c r="AW32" s="24" t="str">
-        <f t="shared" ca="1" si="44"/>
+        <f t="shared" ca="1" si="45"/>
         <v/>
       </c>
       <c r="AX32" s="24" t="str">
-        <f t="shared" ca="1" si="44"/>
+        <f t="shared" ca="1" si="45"/>
         <v/>
       </c>
       <c r="AY32" s="24" t="str">
-        <f t="shared" ca="1" si="44"/>
+        <f t="shared" ca="1" si="45"/>
         <v/>
       </c>
       <c r="AZ32" s="24" t="str">
-        <f t="shared" ca="1" si="44"/>
+        <f t="shared" ca="1" si="45"/>
         <v/>
       </c>
       <c r="BA32" s="24" t="str">
-        <f t="shared" ca="1" si="44"/>
+        <f t="shared" ca="1" si="45"/>
         <v/>
       </c>
       <c r="BB32" s="24" t="str">
-        <f t="shared" ca="1" si="44"/>
+        <f t="shared" ca="1" si="45"/>
         <v/>
       </c>
       <c r="BC32" s="24" t="str">
-        <f t="shared" ca="1" si="44"/>
+        <f t="shared" ca="1" si="45"/>
         <v/>
       </c>
       <c r="BD32" s="24" t="str">
-        <f t="shared" ca="1" si="44"/>
+        <f t="shared" ca="1" si="45"/>
         <v/>
       </c>
       <c r="BE32" s="24" t="str">
-        <f t="shared" ca="1" si="44"/>
+        <f t="shared" ca="1" si="45"/>
         <v/>
       </c>
       <c r="BF32" s="24" t="str">
-        <f t="shared" ca="1" si="44"/>
+        <f t="shared" ca="1" si="45"/>
         <v/>
       </c>
       <c r="BG32" s="24" t="str">
-        <f t="shared" ca="1" si="44"/>
+        <f t="shared" ca="1" si="45"/>
         <v/>
       </c>
       <c r="BH32" s="24" t="str">
-        <f t="shared" ca="1" si="44"/>
+        <f t="shared" ca="1" si="45"/>
         <v/>
       </c>
       <c r="BI32" s="24" t="str">
-        <f t="shared" ca="1" si="44"/>
+        <f t="shared" ca="1" si="45"/>
         <v/>
       </c>
       <c r="BJ32" s="24" t="str">
-        <f t="shared" ca="1" si="44"/>
+        <f t="shared" ca="1" si="45"/>
         <v/>
       </c>
       <c r="BK32" s="24" t="str">
-        <f t="shared" ca="1" si="44"/>
+        <f t="shared" ca="1" si="45"/>
         <v/>
       </c>
       <c r="BL32" s="24" t="str">
-        <f t="shared" ca="1" si="44"/>
+        <f t="shared" ca="1" si="45"/>
         <v/>
       </c>
     </row>
@@ -10237,233 +10316,233 @@
       </c>
       <c r="E33" s="55"/>
       <c r="F33" s="56">
-        <f>F28+22</f>
+        <f t="shared" si="29"/>
         <v>46190</v>
       </c>
       <c r="G33" s="57"/>
       <c r="H33" s="54"/>
       <c r="I33" s="24" t="str">
-        <f t="shared" ref="I33:AN33" ca="1" si="45">IF(AND($C31="Objectif",I$7&gt;=$F31,I$7&lt;=$F31+$G31-1),2,IF(AND($C31="Jalon",I$7&gt;=$F31,I$7&lt;=$F31+$G31-1),1,""))</f>
+        <f t="shared" ref="I33:AN33" ca="1" si="46">IF(AND($C31="Objectif",I$7&gt;=$F31,I$7&lt;=$F31+$G31-1),2,IF(AND($C31="Jalon",I$7&gt;=$F31,I$7&lt;=$F31+$G31-1),1,""))</f>
         <v/>
       </c>
       <c r="J33" s="24" t="str">
-        <f t="shared" ca="1" si="45"/>
+        <f t="shared" ca="1" si="46"/>
         <v/>
       </c>
       <c r="K33" s="24" t="str">
-        <f t="shared" ca="1" si="45"/>
+        <f t="shared" ca="1" si="46"/>
         <v/>
       </c>
       <c r="L33" s="24" t="str">
-        <f t="shared" ca="1" si="45"/>
+        <f t="shared" ca="1" si="46"/>
         <v/>
       </c>
       <c r="M33" s="24" t="str">
-        <f t="shared" ca="1" si="45"/>
+        <f t="shared" ca="1" si="46"/>
         <v/>
       </c>
       <c r="N33" s="24" t="str">
-        <f t="shared" ca="1" si="45"/>
+        <f t="shared" ca="1" si="46"/>
         <v/>
       </c>
       <c r="O33" s="24" t="str">
-        <f t="shared" ca="1" si="45"/>
+        <f t="shared" ca="1" si="46"/>
         <v/>
       </c>
       <c r="P33" s="24" t="str">
-        <f t="shared" ca="1" si="45"/>
+        <f t="shared" ca="1" si="46"/>
         <v/>
       </c>
       <c r="Q33" s="24" t="str">
-        <f t="shared" ca="1" si="45"/>
+        <f t="shared" ca="1" si="46"/>
         <v/>
       </c>
       <c r="R33" s="24" t="str">
-        <f t="shared" ca="1" si="45"/>
+        <f t="shared" ca="1" si="46"/>
         <v/>
       </c>
       <c r="S33" s="24" t="str">
-        <f t="shared" ca="1" si="45"/>
+        <f t="shared" ca="1" si="46"/>
         <v/>
       </c>
       <c r="T33" s="24" t="str">
-        <f t="shared" ca="1" si="45"/>
+        <f t="shared" ca="1" si="46"/>
         <v/>
       </c>
       <c r="U33" s="24" t="str">
-        <f t="shared" ca="1" si="45"/>
+        <f t="shared" ca="1" si="46"/>
         <v/>
       </c>
       <c r="V33" s="24" t="str">
-        <f t="shared" ca="1" si="45"/>
+        <f t="shared" ca="1" si="46"/>
         <v/>
       </c>
       <c r="W33" s="24" t="str">
-        <f t="shared" ca="1" si="45"/>
+        <f t="shared" ca="1" si="46"/>
         <v/>
       </c>
       <c r="X33" s="24" t="str">
-        <f t="shared" ca="1" si="45"/>
+        <f t="shared" ca="1" si="46"/>
         <v/>
       </c>
       <c r="Y33" s="24" t="str">
-        <f t="shared" ca="1" si="45"/>
+        <f t="shared" ca="1" si="46"/>
         <v/>
       </c>
       <c r="Z33" s="24" t="str">
-        <f t="shared" ca="1" si="45"/>
+        <f t="shared" ca="1" si="46"/>
         <v/>
       </c>
       <c r="AA33" s="24" t="str">
-        <f t="shared" ca="1" si="45"/>
+        <f t="shared" ca="1" si="46"/>
         <v/>
       </c>
       <c r="AB33" s="24" t="str">
-        <f t="shared" ca="1" si="45"/>
+        <f t="shared" ca="1" si="46"/>
         <v/>
       </c>
       <c r="AC33" s="24" t="str">
-        <f t="shared" ca="1" si="45"/>
+        <f t="shared" ca="1" si="46"/>
         <v/>
       </c>
       <c r="AD33" s="24" t="str">
-        <f t="shared" ca="1" si="45"/>
+        <f t="shared" ca="1" si="46"/>
         <v/>
       </c>
       <c r="AE33" s="24" t="str">
-        <f t="shared" ca="1" si="45"/>
+        <f t="shared" ca="1" si="46"/>
         <v/>
       </c>
       <c r="AF33" s="24" t="str">
-        <f t="shared" ca="1" si="45"/>
+        <f t="shared" ca="1" si="46"/>
         <v/>
       </c>
       <c r="AG33" s="24" t="str">
-        <f t="shared" ca="1" si="45"/>
+        <f t="shared" ca="1" si="46"/>
         <v/>
       </c>
       <c r="AH33" s="24" t="str">
-        <f t="shared" ca="1" si="45"/>
+        <f t="shared" ca="1" si="46"/>
         <v/>
       </c>
       <c r="AI33" s="24" t="str">
-        <f t="shared" ca="1" si="45"/>
+        <f t="shared" ca="1" si="46"/>
         <v/>
       </c>
       <c r="AJ33" s="24" t="str">
-        <f t="shared" ca="1" si="45"/>
+        <f t="shared" ca="1" si="46"/>
         <v/>
       </c>
       <c r="AK33" s="24" t="str">
-        <f t="shared" ca="1" si="45"/>
+        <f t="shared" ca="1" si="46"/>
         <v/>
       </c>
       <c r="AL33" s="24" t="str">
-        <f t="shared" ca="1" si="45"/>
+        <f t="shared" ca="1" si="46"/>
         <v/>
       </c>
       <c r="AM33" s="24" t="str">
-        <f t="shared" ca="1" si="45"/>
+        <f t="shared" ca="1" si="46"/>
         <v/>
       </c>
       <c r="AN33" s="24" t="str">
-        <f t="shared" ca="1" si="45"/>
+        <f t="shared" ca="1" si="46"/>
         <v/>
       </c>
       <c r="AO33" s="24" t="str">
-        <f t="shared" ref="AO33:BL33" ca="1" si="46">IF(AND($C31="Objectif",AO$7&gt;=$F31,AO$7&lt;=$F31+$G31-1),2,IF(AND($C31="Jalon",AO$7&gt;=$F31,AO$7&lt;=$F31+$G31-1),1,""))</f>
+        <f t="shared" ref="AO33:BL33" ca="1" si="47">IF(AND($C31="Objectif",AO$7&gt;=$F31,AO$7&lt;=$F31+$G31-1),2,IF(AND($C31="Jalon",AO$7&gt;=$F31,AO$7&lt;=$F31+$G31-1),1,""))</f>
         <v/>
       </c>
       <c r="AP33" s="24" t="str">
-        <f t="shared" ca="1" si="46"/>
+        <f t="shared" ca="1" si="47"/>
         <v/>
       </c>
       <c r="AQ33" s="24" t="str">
-        <f t="shared" ca="1" si="46"/>
+        <f t="shared" ca="1" si="47"/>
         <v/>
       </c>
       <c r="AR33" s="24" t="str">
-        <f t="shared" ca="1" si="46"/>
+        <f t="shared" ca="1" si="47"/>
         <v/>
       </c>
       <c r="AS33" s="24" t="str">
-        <f t="shared" ca="1" si="46"/>
+        <f t="shared" ca="1" si="47"/>
         <v/>
       </c>
       <c r="AT33" s="24" t="str">
-        <f t="shared" ca="1" si="46"/>
+        <f t="shared" ca="1" si="47"/>
         <v/>
       </c>
       <c r="AU33" s="24" t="str">
-        <f t="shared" ca="1" si="46"/>
+        <f t="shared" ca="1" si="47"/>
         <v/>
       </c>
       <c r="AV33" s="24" t="str">
-        <f t="shared" ca="1" si="46"/>
+        <f t="shared" ca="1" si="47"/>
         <v/>
       </c>
       <c r="AW33" s="24" t="str">
-        <f t="shared" ca="1" si="46"/>
+        <f t="shared" ca="1" si="47"/>
         <v/>
       </c>
       <c r="AX33" s="24" t="str">
-        <f t="shared" ca="1" si="46"/>
+        <f t="shared" ca="1" si="47"/>
         <v/>
       </c>
       <c r="AY33" s="24" t="str">
-        <f t="shared" ca="1" si="46"/>
+        <f t="shared" ca="1" si="47"/>
         <v/>
       </c>
       <c r="AZ33" s="24" t="str">
-        <f t="shared" ca="1" si="46"/>
+        <f t="shared" ca="1" si="47"/>
         <v/>
       </c>
       <c r="BA33" s="24" t="str">
-        <f t="shared" ca="1" si="46"/>
+        <f t="shared" ca="1" si="47"/>
         <v/>
       </c>
       <c r="BB33" s="24" t="str">
-        <f t="shared" ca="1" si="46"/>
+        <f t="shared" ca="1" si="47"/>
         <v/>
       </c>
       <c r="BC33" s="24" t="str">
-        <f t="shared" ca="1" si="46"/>
+        <f t="shared" ca="1" si="47"/>
         <v/>
       </c>
       <c r="BD33" s="24" t="str">
-        <f t="shared" ca="1" si="46"/>
+        <f t="shared" ca="1" si="47"/>
         <v/>
       </c>
       <c r="BE33" s="24" t="str">
-        <f t="shared" ca="1" si="46"/>
+        <f t="shared" ca="1" si="47"/>
         <v/>
       </c>
       <c r="BF33" s="24" t="str">
-        <f t="shared" ca="1" si="46"/>
+        <f t="shared" ca="1" si="47"/>
         <v/>
       </c>
       <c r="BG33" s="24" t="str">
-        <f t="shared" ca="1" si="46"/>
+        <f t="shared" ca="1" si="47"/>
         <v/>
       </c>
       <c r="BH33" s="24" t="str">
-        <f t="shared" ca="1" si="46"/>
+        <f t="shared" ca="1" si="47"/>
         <v/>
       </c>
       <c r="BI33" s="24" t="str">
-        <f t="shared" ca="1" si="46"/>
+        <f t="shared" ca="1" si="47"/>
         <v/>
       </c>
       <c r="BJ33" s="24" t="str">
-        <f t="shared" ca="1" si="46"/>
+        <f t="shared" ca="1" si="47"/>
         <v/>
       </c>
       <c r="BK33" s="24" t="str">
-        <f t="shared" ca="1" si="46"/>
+        <f t="shared" ca="1" si="47"/>
         <v/>
       </c>
       <c r="BL33" s="24" t="str">
-        <f t="shared" ca="1" si="46"/>
+        <f t="shared" ca="1" si="47"/>
         <v/>
       </c>
     </row>
@@ -10480,476 +10559,476 @@
       </c>
       <c r="E34" s="69"/>
       <c r="F34" s="56">
-        <f>F29+22</f>
+        <f t="shared" si="29"/>
         <v>46205</v>
       </c>
       <c r="G34" s="80"/>
       <c r="H34" s="54"/>
       <c r="I34" s="24" t="str">
-        <f t="shared" ref="I34:AN34" ca="1" si="47">IF(AND($C32="Objectif",I$7&gt;=$F32,I$7&lt;=$F32+$G32-1),2,IF(AND($C32="Jalon",I$7&gt;=$F32,I$7&lt;=$F32+$G32-1),1,""))</f>
+        <f t="shared" ref="I34:AN34" ca="1" si="48">IF(AND($C32="Objectif",I$7&gt;=$F32,I$7&lt;=$F32+$G32-1),2,IF(AND($C32="Jalon",I$7&gt;=$F32,I$7&lt;=$F32+$G32-1),1,""))</f>
         <v/>
       </c>
       <c r="J34" s="24" t="str">
-        <f t="shared" ca="1" si="47"/>
+        <f t="shared" ca="1" si="48"/>
         <v/>
       </c>
       <c r="K34" s="24" t="str">
-        <f t="shared" ca="1" si="47"/>
+        <f t="shared" ca="1" si="48"/>
         <v/>
       </c>
       <c r="L34" s="24" t="str">
-        <f t="shared" ca="1" si="47"/>
+        <f t="shared" ca="1" si="48"/>
         <v/>
       </c>
       <c r="M34" s="24" t="str">
-        <f t="shared" ca="1" si="47"/>
+        <f t="shared" ca="1" si="48"/>
         <v/>
       </c>
       <c r="N34" s="24" t="str">
-        <f t="shared" ca="1" si="47"/>
+        <f t="shared" ca="1" si="48"/>
         <v/>
       </c>
       <c r="O34" s="24" t="str">
-        <f t="shared" ca="1" si="47"/>
+        <f t="shared" ca="1" si="48"/>
         <v/>
       </c>
       <c r="P34" s="24" t="str">
-        <f t="shared" ca="1" si="47"/>
+        <f t="shared" ca="1" si="48"/>
         <v/>
       </c>
       <c r="Q34" s="24" t="str">
-        <f t="shared" ca="1" si="47"/>
+        <f t="shared" ca="1" si="48"/>
         <v/>
       </c>
       <c r="R34" s="24" t="str">
-        <f t="shared" ca="1" si="47"/>
+        <f t="shared" ca="1" si="48"/>
         <v/>
       </c>
       <c r="S34" s="24" t="str">
-        <f t="shared" ca="1" si="47"/>
+        <f t="shared" ca="1" si="48"/>
         <v/>
       </c>
       <c r="T34" s="24" t="str">
-        <f t="shared" ca="1" si="47"/>
+        <f t="shared" ca="1" si="48"/>
         <v/>
       </c>
       <c r="U34" s="24" t="str">
-        <f t="shared" ca="1" si="47"/>
+        <f t="shared" ca="1" si="48"/>
         <v/>
       </c>
       <c r="V34" s="24" t="str">
-        <f t="shared" ca="1" si="47"/>
+        <f t="shared" ca="1" si="48"/>
         <v/>
       </c>
       <c r="W34" s="24" t="str">
-        <f t="shared" ca="1" si="47"/>
+        <f t="shared" ca="1" si="48"/>
         <v/>
       </c>
       <c r="X34" s="24" t="str">
-        <f t="shared" ca="1" si="47"/>
+        <f t="shared" ca="1" si="48"/>
         <v/>
       </c>
       <c r="Y34" s="24" t="str">
-        <f t="shared" ca="1" si="47"/>
+        <f t="shared" ca="1" si="48"/>
         <v/>
       </c>
       <c r="Z34" s="24" t="str">
-        <f t="shared" ca="1" si="47"/>
+        <f t="shared" ca="1" si="48"/>
         <v/>
       </c>
       <c r="AA34" s="24" t="str">
-        <f t="shared" ca="1" si="47"/>
+        <f t="shared" ca="1" si="48"/>
         <v/>
       </c>
       <c r="AB34" s="24" t="str">
-        <f t="shared" ca="1" si="47"/>
+        <f t="shared" ca="1" si="48"/>
         <v/>
       </c>
       <c r="AC34" s="24" t="str">
-        <f t="shared" ca="1" si="47"/>
+        <f t="shared" ca="1" si="48"/>
         <v/>
       </c>
       <c r="AD34" s="24" t="str">
-        <f t="shared" ca="1" si="47"/>
+        <f t="shared" ca="1" si="48"/>
         <v/>
       </c>
       <c r="AE34" s="24" t="str">
-        <f t="shared" ca="1" si="47"/>
+        <f t="shared" ca="1" si="48"/>
         <v/>
       </c>
       <c r="AF34" s="24" t="str">
-        <f t="shared" ca="1" si="47"/>
+        <f t="shared" ca="1" si="48"/>
         <v/>
       </c>
       <c r="AG34" s="24" t="str">
-        <f t="shared" ca="1" si="47"/>
+        <f t="shared" ca="1" si="48"/>
         <v/>
       </c>
       <c r="AH34" s="24" t="str">
-        <f t="shared" ca="1" si="47"/>
+        <f t="shared" ca="1" si="48"/>
         <v/>
       </c>
       <c r="AI34" s="24" t="str">
-        <f t="shared" ca="1" si="47"/>
+        <f t="shared" ca="1" si="48"/>
         <v/>
       </c>
       <c r="AJ34" s="24" t="str">
-        <f t="shared" ca="1" si="47"/>
+        <f t="shared" ca="1" si="48"/>
         <v/>
       </c>
       <c r="AK34" s="24" t="str">
-        <f t="shared" ca="1" si="47"/>
+        <f t="shared" ca="1" si="48"/>
         <v/>
       </c>
       <c r="AL34" s="24" t="str">
-        <f t="shared" ca="1" si="47"/>
+        <f t="shared" ca="1" si="48"/>
         <v/>
       </c>
       <c r="AM34" s="24" t="str">
-        <f t="shared" ca="1" si="47"/>
+        <f t="shared" ca="1" si="48"/>
         <v/>
       </c>
       <c r="AN34" s="24" t="str">
-        <f t="shared" ca="1" si="47"/>
+        <f t="shared" ca="1" si="48"/>
         <v/>
       </c>
       <c r="AO34" s="24" t="str">
-        <f t="shared" ref="AO34:BL34" ca="1" si="48">IF(AND($C32="Objectif",AO$7&gt;=$F32,AO$7&lt;=$F32+$G32-1),2,IF(AND($C32="Jalon",AO$7&gt;=$F32,AO$7&lt;=$F32+$G32-1),1,""))</f>
+        <f t="shared" ref="AO34:BL34" ca="1" si="49">IF(AND($C32="Objectif",AO$7&gt;=$F32,AO$7&lt;=$F32+$G32-1),2,IF(AND($C32="Jalon",AO$7&gt;=$F32,AO$7&lt;=$F32+$G32-1),1,""))</f>
         <v/>
       </c>
       <c r="AP34" s="24" t="str">
-        <f t="shared" ca="1" si="48"/>
+        <f t="shared" ca="1" si="49"/>
         <v/>
       </c>
       <c r="AQ34" s="24" t="str">
-        <f t="shared" ca="1" si="48"/>
+        <f t="shared" ca="1" si="49"/>
         <v/>
       </c>
       <c r="AR34" s="24" t="str">
-        <f t="shared" ca="1" si="48"/>
+        <f t="shared" ca="1" si="49"/>
         <v/>
       </c>
       <c r="AS34" s="24" t="str">
-        <f t="shared" ca="1" si="48"/>
+        <f t="shared" ca="1" si="49"/>
         <v/>
       </c>
       <c r="AT34" s="24" t="str">
-        <f t="shared" ca="1" si="48"/>
+        <f t="shared" ca="1" si="49"/>
         <v/>
       </c>
       <c r="AU34" s="24" t="str">
-        <f t="shared" ca="1" si="48"/>
+        <f t="shared" ca="1" si="49"/>
         <v/>
       </c>
       <c r="AV34" s="24" t="str">
-        <f t="shared" ca="1" si="48"/>
+        <f t="shared" ca="1" si="49"/>
         <v/>
       </c>
       <c r="AW34" s="24" t="str">
-        <f t="shared" ca="1" si="48"/>
+        <f t="shared" ca="1" si="49"/>
         <v/>
       </c>
       <c r="AX34" s="24" t="str">
-        <f t="shared" ca="1" si="48"/>
+        <f t="shared" ca="1" si="49"/>
         <v/>
       </c>
       <c r="AY34" s="24" t="str">
-        <f t="shared" ca="1" si="48"/>
+        <f t="shared" ca="1" si="49"/>
         <v/>
       </c>
       <c r="AZ34" s="24" t="str">
-        <f t="shared" ca="1" si="48"/>
+        <f t="shared" ca="1" si="49"/>
         <v/>
       </c>
       <c r="BA34" s="24" t="str">
-        <f t="shared" ca="1" si="48"/>
+        <f t="shared" ca="1" si="49"/>
         <v/>
       </c>
       <c r="BB34" s="24" t="str">
-        <f t="shared" ca="1" si="48"/>
+        <f t="shared" ca="1" si="49"/>
         <v/>
       </c>
       <c r="BC34" s="24" t="str">
-        <f t="shared" ca="1" si="48"/>
+        <f t="shared" ca="1" si="49"/>
         <v/>
       </c>
       <c r="BD34" s="24" t="str">
-        <f t="shared" ca="1" si="48"/>
+        <f t="shared" ca="1" si="49"/>
         <v/>
       </c>
       <c r="BE34" s="24" t="str">
-        <f t="shared" ca="1" si="48"/>
+        <f t="shared" ca="1" si="49"/>
         <v/>
       </c>
       <c r="BF34" s="24" t="str">
-        <f t="shared" ca="1" si="48"/>
+        <f t="shared" ca="1" si="49"/>
         <v/>
       </c>
       <c r="BG34" s="24" t="str">
-        <f t="shared" ca="1" si="48"/>
+        <f t="shared" ca="1" si="49"/>
         <v/>
       </c>
       <c r="BH34" s="24" t="str">
-        <f t="shared" ca="1" si="48"/>
+        <f t="shared" ca="1" si="49"/>
         <v/>
       </c>
       <c r="BI34" s="24" t="str">
-        <f t="shared" ca="1" si="48"/>
+        <f t="shared" ca="1" si="49"/>
         <v/>
       </c>
       <c r="BJ34" s="24" t="str">
-        <f t="shared" ca="1" si="48"/>
+        <f t="shared" ca="1" si="49"/>
         <v/>
       </c>
       <c r="BK34" s="24" t="str">
-        <f t="shared" ca="1" si="48"/>
+        <f t="shared" ca="1" si="49"/>
         <v/>
       </c>
       <c r="BL34" s="24" t="str">
-        <f t="shared" ca="1" si="48"/>
+        <f t="shared" ca="1" si="49"/>
         <v/>
       </c>
     </row>
     <row r="35" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="9"/>
-      <c r="B35" s="142" t="s">
+      <c r="B35" s="124" t="s">
         <v>71</v>
       </c>
-      <c r="C35" s="143" t="s">
+      <c r="C35" s="81" t="s">
         <v>25</v>
       </c>
-      <c r="D35" s="144" t="s">
+      <c r="D35" s="125" t="s">
         <v>67</v>
       </c>
-      <c r="E35" s="145"/>
+      <c r="E35"/>
       <c r="F35" s="56">
-        <f>F30+22</f>
+        <f t="shared" si="29"/>
         <v>46226</v>
       </c>
-      <c r="G35" s="146"/>
+      <c r="G35" s="126"/>
       <c r="H35" s="54"/>
       <c r="I35" s="24" t="str">
-        <f t="shared" ref="I35:AN35" ca="1" si="49">IF(AND($C33="Objectif",I$7&gt;=$F33,I$7&lt;=$F33+$G33-1),2,IF(AND($C33="Jalon",I$7&gt;=$F33,I$7&lt;=$F33+$G33-1),1,""))</f>
+        <f t="shared" ref="I35:AN35" ca="1" si="50">IF(AND($C33="Objectif",I$7&gt;=$F33,I$7&lt;=$F33+$G33-1),2,IF(AND($C33="Jalon",I$7&gt;=$F33,I$7&lt;=$F33+$G33-1),1,""))</f>
         <v/>
       </c>
       <c r="J35" s="24" t="str">
-        <f t="shared" ca="1" si="49"/>
+        <f t="shared" ca="1" si="50"/>
         <v/>
       </c>
       <c r="K35" s="24" t="str">
-        <f t="shared" ca="1" si="49"/>
+        <f t="shared" ca="1" si="50"/>
         <v/>
       </c>
       <c r="L35" s="24" t="str">
-        <f t="shared" ca="1" si="49"/>
+        <f t="shared" ca="1" si="50"/>
         <v/>
       </c>
       <c r="M35" s="24" t="str">
-        <f t="shared" ca="1" si="49"/>
+        <f t="shared" ca="1" si="50"/>
         <v/>
       </c>
       <c r="N35" s="24" t="str">
-        <f t="shared" ca="1" si="49"/>
+        <f t="shared" ca="1" si="50"/>
         <v/>
       </c>
       <c r="O35" s="24" t="str">
-        <f t="shared" ca="1" si="49"/>
+        <f t="shared" ca="1" si="50"/>
         <v/>
       </c>
       <c r="P35" s="24" t="str">
-        <f t="shared" ca="1" si="49"/>
+        <f t="shared" ca="1" si="50"/>
         <v/>
       </c>
       <c r="Q35" s="24" t="str">
-        <f t="shared" ca="1" si="49"/>
+        <f t="shared" ca="1" si="50"/>
         <v/>
       </c>
       <c r="R35" s="24" t="str">
-        <f t="shared" ca="1" si="49"/>
+        <f t="shared" ca="1" si="50"/>
         <v/>
       </c>
       <c r="S35" s="24" t="str">
-        <f t="shared" ca="1" si="49"/>
+        <f t="shared" ca="1" si="50"/>
         <v/>
       </c>
       <c r="T35" s="24" t="str">
-        <f t="shared" ca="1" si="49"/>
+        <f t="shared" ca="1" si="50"/>
         <v/>
       </c>
       <c r="U35" s="24" t="str">
-        <f t="shared" ca="1" si="49"/>
+        <f t="shared" ca="1" si="50"/>
         <v/>
       </c>
       <c r="V35" s="24" t="str">
-        <f t="shared" ca="1" si="49"/>
+        <f t="shared" ca="1" si="50"/>
         <v/>
       </c>
       <c r="W35" s="24" t="str">
-        <f t="shared" ca="1" si="49"/>
+        <f t="shared" ca="1" si="50"/>
         <v/>
       </c>
       <c r="X35" s="24" t="str">
-        <f t="shared" ca="1" si="49"/>
+        <f t="shared" ca="1" si="50"/>
         <v/>
       </c>
       <c r="Y35" s="24" t="str">
-        <f t="shared" ca="1" si="49"/>
+        <f t="shared" ca="1" si="50"/>
         <v/>
       </c>
       <c r="Z35" s="24" t="str">
-        <f t="shared" ca="1" si="49"/>
+        <f t="shared" ca="1" si="50"/>
         <v/>
       </c>
       <c r="AA35" s="24" t="str">
-        <f t="shared" ca="1" si="49"/>
+        <f t="shared" ca="1" si="50"/>
         <v/>
       </c>
       <c r="AB35" s="24" t="str">
-        <f t="shared" ca="1" si="49"/>
+        <f t="shared" ca="1" si="50"/>
         <v/>
       </c>
       <c r="AC35" s="24" t="str">
-        <f t="shared" ca="1" si="49"/>
+        <f t="shared" ca="1" si="50"/>
         <v/>
       </c>
       <c r="AD35" s="24" t="str">
-        <f t="shared" ca="1" si="49"/>
+        <f t="shared" ca="1" si="50"/>
         <v/>
       </c>
       <c r="AE35" s="24" t="str">
-        <f t="shared" ca="1" si="49"/>
+        <f t="shared" ca="1" si="50"/>
         <v/>
       </c>
       <c r="AF35" s="24" t="str">
-        <f t="shared" ca="1" si="49"/>
+        <f t="shared" ca="1" si="50"/>
         <v/>
       </c>
       <c r="AG35" s="24" t="str">
-        <f t="shared" ca="1" si="49"/>
+        <f t="shared" ca="1" si="50"/>
         <v/>
       </c>
       <c r="AH35" s="24" t="str">
-        <f t="shared" ca="1" si="49"/>
+        <f t="shared" ca="1" si="50"/>
         <v/>
       </c>
       <c r="AI35" s="24" t="str">
-        <f t="shared" ca="1" si="49"/>
+        <f t="shared" ca="1" si="50"/>
         <v/>
       </c>
       <c r="AJ35" s="24" t="str">
-        <f t="shared" ca="1" si="49"/>
+        <f t="shared" ca="1" si="50"/>
         <v/>
       </c>
       <c r="AK35" s="24" t="str">
-        <f t="shared" ca="1" si="49"/>
+        <f t="shared" ca="1" si="50"/>
         <v/>
       </c>
       <c r="AL35" s="24" t="str">
-        <f t="shared" ca="1" si="49"/>
+        <f t="shared" ca="1" si="50"/>
         <v/>
       </c>
       <c r="AM35" s="24" t="str">
-        <f t="shared" ca="1" si="49"/>
+        <f t="shared" ca="1" si="50"/>
         <v/>
       </c>
       <c r="AN35" s="24" t="str">
-        <f t="shared" ca="1" si="49"/>
+        <f t="shared" ca="1" si="50"/>
         <v/>
       </c>
       <c r="AO35" s="24" t="str">
-        <f t="shared" ref="AO35:BL35" ca="1" si="50">IF(AND($C33="Objectif",AO$7&gt;=$F33,AO$7&lt;=$F33+$G33-1),2,IF(AND($C33="Jalon",AO$7&gt;=$F33,AO$7&lt;=$F33+$G33-1),1,""))</f>
+        <f t="shared" ref="AO35:BL35" ca="1" si="51">IF(AND($C33="Objectif",AO$7&gt;=$F33,AO$7&lt;=$F33+$G33-1),2,IF(AND($C33="Jalon",AO$7&gt;=$F33,AO$7&lt;=$F33+$G33-1),1,""))</f>
         <v/>
       </c>
       <c r="AP35" s="24" t="str">
-        <f t="shared" ca="1" si="50"/>
+        <f t="shared" ca="1" si="51"/>
         <v/>
       </c>
       <c r="AQ35" s="24" t="str">
-        <f t="shared" ca="1" si="50"/>
+        <f t="shared" ca="1" si="51"/>
         <v/>
       </c>
       <c r="AR35" s="24" t="str">
-        <f t="shared" ca="1" si="50"/>
+        <f t="shared" ca="1" si="51"/>
         <v/>
       </c>
       <c r="AS35" s="24" t="str">
-        <f t="shared" ca="1" si="50"/>
+        <f t="shared" ca="1" si="51"/>
         <v/>
       </c>
       <c r="AT35" s="24" t="str">
-        <f t="shared" ca="1" si="50"/>
+        <f t="shared" ca="1" si="51"/>
         <v/>
       </c>
       <c r="AU35" s="24" t="str">
-        <f t="shared" ca="1" si="50"/>
+        <f t="shared" ca="1" si="51"/>
         <v/>
       </c>
       <c r="AV35" s="24" t="str">
-        <f t="shared" ca="1" si="50"/>
+        <f t="shared" ca="1" si="51"/>
         <v/>
       </c>
       <c r="AW35" s="24" t="str">
-        <f t="shared" ca="1" si="50"/>
+        <f t="shared" ca="1" si="51"/>
         <v/>
       </c>
       <c r="AX35" s="24" t="str">
-        <f t="shared" ca="1" si="50"/>
+        <f t="shared" ca="1" si="51"/>
         <v/>
       </c>
       <c r="AY35" s="24" t="str">
-        <f t="shared" ca="1" si="50"/>
+        <f t="shared" ca="1" si="51"/>
         <v/>
       </c>
       <c r="AZ35" s="24" t="str">
-        <f t="shared" ca="1" si="50"/>
+        <f t="shared" ca="1" si="51"/>
         <v/>
       </c>
       <c r="BA35" s="24" t="str">
-        <f t="shared" ca="1" si="50"/>
+        <f t="shared" ca="1" si="51"/>
         <v/>
       </c>
       <c r="BB35" s="24" t="str">
-        <f t="shared" ca="1" si="50"/>
+        <f t="shared" ca="1" si="51"/>
         <v/>
       </c>
       <c r="BC35" s="24" t="str">
-        <f t="shared" ca="1" si="50"/>
+        <f t="shared" ca="1" si="51"/>
         <v/>
       </c>
       <c r="BD35" s="24" t="str">
-        <f t="shared" ca="1" si="50"/>
+        <f t="shared" ca="1" si="51"/>
         <v/>
       </c>
       <c r="BE35" s="24" t="str">
-        <f t="shared" ca="1" si="50"/>
+        <f t="shared" ca="1" si="51"/>
         <v/>
       </c>
       <c r="BF35" s="24" t="str">
-        <f t="shared" ca="1" si="50"/>
+        <f t="shared" ca="1" si="51"/>
         <v/>
       </c>
       <c r="BG35" s="24" t="str">
-        <f t="shared" ca="1" si="50"/>
+        <f t="shared" ca="1" si="51"/>
         <v/>
       </c>
       <c r="BH35" s="24" t="str">
-        <f t="shared" ca="1" si="50"/>
+        <f t="shared" ca="1" si="51"/>
         <v/>
       </c>
       <c r="BI35" s="24" t="str">
-        <f t="shared" ca="1" si="50"/>
+        <f t="shared" ca="1" si="51"/>
         <v/>
       </c>
       <c r="BJ35" s="24" t="str">
-        <f t="shared" ca="1" si="50"/>
+        <f t="shared" ca="1" si="51"/>
         <v/>
       </c>
       <c r="BK35" s="24" t="str">
-        <f t="shared" ca="1" si="50"/>
+        <f t="shared" ca="1" si="51"/>
         <v/>
       </c>
       <c r="BL35" s="24" t="str">
-        <f t="shared" ca="1" si="50"/>
+        <f t="shared" ca="1" si="51"/>
         <v/>
       </c>
       <c r="BM35" s="83"/>
@@ -11050,107 +11129,107 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I6:AM6">
-    <cfRule type="expression" dxfId="54" priority="4">
+    <cfRule type="expression" dxfId="46" priority="4">
       <formula>I$7&lt;=EOMONTH($I$7,0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I10:BL16">
-    <cfRule type="expression" dxfId="53" priority="7" stopIfTrue="1">
+    <cfRule type="expression" dxfId="45" priority="7" stopIfTrue="1">
       <formula>AND($C10="Risque faible",I$7&gt;=$F10,I$7&lt;=$F10+$G10-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="52" priority="8" stopIfTrue="1">
+    <cfRule type="expression" dxfId="44" priority="8" stopIfTrue="1">
       <formula>AND($C10="Risque élevé",I$7&gt;=$F10,I$7&lt;=$F10+$G10-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="51" priority="9" stopIfTrue="1">
+    <cfRule type="expression" dxfId="43" priority="9" stopIfTrue="1">
       <formula>AND($C10="En bonne voie",I$7&gt;=$F10,I$7&lt;=$F10+$G10-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="50" priority="10" stopIfTrue="1">
+    <cfRule type="expression" dxfId="42" priority="10" stopIfTrue="1">
       <formula>AND($C10="Risque moyen",I$7&gt;=$F10,I$7&lt;=$F10+$G10-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="49" priority="11" stopIfTrue="1">
+    <cfRule type="expression" dxfId="41" priority="11" stopIfTrue="1">
       <formula>AND(LEN($C10)=0,I$7&gt;=$F10,I$7&lt;=$F10+$G10-1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I17:BL17">
-    <cfRule type="expression" dxfId="48" priority="30" stopIfTrue="1">
+    <cfRule type="expression" dxfId="40" priority="30" stopIfTrue="1">
       <formula>AND(#REF!="En bonne voie",I$7&gt;=#REF!,I$7&lt;=#REF!+#REF!-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="47" priority="29" stopIfTrue="1">
+    <cfRule type="expression" dxfId="39" priority="29" stopIfTrue="1">
       <formula>AND(#REF!="Risque élevé",I$7&gt;=#REF!,I$7&lt;=#REF!+#REF!-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="46" priority="28" stopIfTrue="1">
+    <cfRule type="expression" dxfId="38" priority="28" stopIfTrue="1">
       <formula>AND(#REF!="Risque faible",I$7&gt;=#REF!,I$7&lt;=#REF!+#REF!-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="45" priority="31" stopIfTrue="1">
+    <cfRule type="expression" dxfId="37" priority="31" stopIfTrue="1">
       <formula>AND(#REF!="Risque moyen",I$7&gt;=#REF!,I$7&lt;=#REF!+#REF!-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="44" priority="32" stopIfTrue="1">
+    <cfRule type="expression" dxfId="36" priority="32" stopIfTrue="1">
       <formula>AND(LEN(#REF!)=0,I$7&gt;=#REF!,I$7&lt;=#REF!+#REF!-1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I18:BL22">
-    <cfRule type="expression" dxfId="43" priority="22" stopIfTrue="1">
+    <cfRule type="expression" dxfId="35" priority="22" stopIfTrue="1">
       <formula>AND($C17="Risque faible",I$7&gt;=$F17,I$7&lt;=$F17+$G17-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="42" priority="23" stopIfTrue="1">
+    <cfRule type="expression" dxfId="34" priority="23" stopIfTrue="1">
       <formula>AND($C17="Risque élevé",I$7&gt;=$F17,I$7&lt;=$F17+$G17-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="41" priority="24" stopIfTrue="1">
+    <cfRule type="expression" dxfId="33" priority="24" stopIfTrue="1">
       <formula>AND($C17="En bonne voie",I$7&gt;=$F17,I$7&lt;=$F17+$G17-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="40" priority="25" stopIfTrue="1">
+    <cfRule type="expression" dxfId="32" priority="25" stopIfTrue="1">
       <formula>AND($C17="Risque moyen",I$7&gt;=$F17,I$7&lt;=$F17+$G17-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="39" priority="26" stopIfTrue="1">
+    <cfRule type="expression" dxfId="31" priority="26" stopIfTrue="1">
       <formula>AND(LEN($C17)=0,I$7&gt;=$F17,I$7&lt;=$F17+$G17-1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I23:BL23">
-    <cfRule type="expression" dxfId="38" priority="50" stopIfTrue="1">
+    <cfRule type="expression" dxfId="30" priority="50" stopIfTrue="1">
       <formula>AND(LEN(#REF!)=0,I$7&gt;=#REF!,I$7&lt;=#REF!+#REF!-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="37" priority="46" stopIfTrue="1">
+    <cfRule type="expression" dxfId="29" priority="46" stopIfTrue="1">
       <formula>AND(#REF!="Risque faible",I$7&gt;=#REF!,I$7&lt;=#REF!+#REF!-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="36" priority="47" stopIfTrue="1">
+    <cfRule type="expression" dxfId="28" priority="47" stopIfTrue="1">
       <formula>AND(#REF!="Risque élevé",I$7&gt;=#REF!,I$7&lt;=#REF!+#REF!-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="35" priority="48" stopIfTrue="1">
+    <cfRule type="expression" dxfId="27" priority="48" stopIfTrue="1">
       <formula>AND(#REF!="En bonne voie",I$7&gt;=#REF!,I$7&lt;=#REF!+#REF!-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="34" priority="49" stopIfTrue="1">
+    <cfRule type="expression" dxfId="26" priority="49" stopIfTrue="1">
       <formula>AND(#REF!="Risque moyen",I$7&gt;=#REF!,I$7&lt;=#REF!+#REF!-1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I24:BL35">
-    <cfRule type="expression" dxfId="33" priority="41" stopIfTrue="1">
+    <cfRule type="expression" dxfId="25" priority="41" stopIfTrue="1">
       <formula>AND($C22="Risque élevé",I$7&gt;=$F22,I$7&lt;=$F22+$G22-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="32" priority="42" stopIfTrue="1">
+    <cfRule type="expression" dxfId="24" priority="42" stopIfTrue="1">
       <formula>AND($C22="En bonne voie",I$7&gt;=$F22,I$7&lt;=$F22+$G22-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="31" priority="43" stopIfTrue="1">
+    <cfRule type="expression" dxfId="23" priority="43" stopIfTrue="1">
       <formula>AND($C22="Risque moyen",I$7&gt;=$F22,I$7&lt;=$F22+$G22-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="44" stopIfTrue="1">
+    <cfRule type="expression" dxfId="22" priority="44" stopIfTrue="1">
       <formula>AND(LEN($C22)=0,I$7&gt;=$F22,I$7&lt;=$F22+$G22-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="29" priority="40" stopIfTrue="1">
+    <cfRule type="expression" dxfId="21" priority="40" stopIfTrue="1">
       <formula>AND($C22="Risque faible",I$7&gt;=$F22,I$7&lt;=$F22+$G22-1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I6:BV6">
-    <cfRule type="expression" dxfId="28" priority="2">
+    <cfRule type="expression" dxfId="20" priority="2">
       <formula>AND(I$7&lt;=EOMONTH($I$7,1),I$7&gt;EOMONTH($I$7,0))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I7:BV7 I8:BL36 BM9:BV9">
-    <cfRule type="expression" dxfId="27" priority="1">
+    <cfRule type="expression" dxfId="19" priority="1">
       <formula>AND(TODAY()&gt;=I$7,TODAY()&lt;J$7)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J6:BV6">
-    <cfRule type="expression" dxfId="26" priority="3">
+    <cfRule type="expression" dxfId="18" priority="3">
       <formula>AND(J$7&lt;=EOMONTH($I$7,2),J$7&gt;EOMONTH($I$7,0),J$7&gt;EOMONTH($I$7,1))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11369,27 +11448,27 @@
     <row r="1" spans="1:68" ht="25.15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="1:68" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="10"/>
-      <c r="B2" s="134" t="s">
+      <c r="B2" s="148" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="134"/>
-      <c r="D2" s="134"/>
-      <c r="E2" s="134"/>
-      <c r="F2" s="134"/>
-      <c r="G2" s="134"/>
-      <c r="H2" s="134"/>
-      <c r="I2" s="135"/>
-      <c r="J2" s="135"/>
-      <c r="K2" s="135"/>
-      <c r="L2" s="135"/>
-      <c r="M2" s="135"/>
-      <c r="N2" s="135"/>
-      <c r="O2" s="136"/>
-      <c r="P2" s="137"/>
-      <c r="Q2" s="137"/>
-      <c r="R2" s="137"/>
-      <c r="S2" s="137"/>
-      <c r="T2" s="137"/>
+      <c r="C2" s="148"/>
+      <c r="D2" s="148"/>
+      <c r="E2" s="148"/>
+      <c r="F2" s="148"/>
+      <c r="G2" s="148"/>
+      <c r="H2" s="148"/>
+      <c r="I2" s="149"/>
+      <c r="J2" s="149"/>
+      <c r="K2" s="149"/>
+      <c r="L2" s="149"/>
+      <c r="M2" s="149"/>
+      <c r="N2" s="149"/>
+      <c r="O2" s="150"/>
+      <c r="P2" s="151"/>
+      <c r="Q2" s="151"/>
+      <c r="R2" s="151"/>
+      <c r="S2" s="151"/>
+      <c r="T2" s="151"/>
       <c r="U2" s="18"/>
       <c r="V2" s="18"/>
       <c r="W2" s="18"/>
@@ -11516,45 +11595,45 @@
         <v>30</v>
       </c>
       <c r="H4" s="27"/>
-      <c r="I4" s="132" t="s">
+      <c r="I4" s="146" t="s">
         <v>25</v>
       </c>
-      <c r="J4" s="132"/>
-      <c r="K4" s="132"/>
-      <c r="L4" s="132"/>
-      <c r="M4" s="132"/>
+      <c r="J4" s="146"/>
+      <c r="K4" s="146"/>
+      <c r="L4" s="146"/>
+      <c r="M4" s="146"/>
       <c r="N4" s="30"/>
-      <c r="O4" s="133" t="s">
+      <c r="O4" s="147" t="s">
         <v>22</v>
       </c>
-      <c r="P4" s="133"/>
-      <c r="Q4" s="133"/>
-      <c r="R4" s="133"/>
-      <c r="S4" s="133"/>
+      <c r="P4" s="147"/>
+      <c r="Q4" s="147"/>
+      <c r="R4" s="147"/>
+      <c r="S4" s="147"/>
       <c r="T4" s="30"/>
-      <c r="U4" s="126" t="s">
+      <c r="U4" s="140" t="s">
         <v>23</v>
       </c>
-      <c r="V4" s="126"/>
-      <c r="W4" s="126"/>
-      <c r="X4" s="126"/>
-      <c r="Y4" s="126"/>
+      <c r="V4" s="140"/>
+      <c r="W4" s="140"/>
+      <c r="X4" s="140"/>
+      <c r="Y4" s="140"/>
       <c r="Z4" s="30"/>
-      <c r="AA4" s="127" t="s">
+      <c r="AA4" s="141" t="s">
         <v>24</v>
       </c>
-      <c r="AB4" s="127"/>
-      <c r="AC4" s="127"/>
-      <c r="AD4" s="127"/>
-      <c r="AE4" s="127"/>
+      <c r="AB4" s="141"/>
+      <c r="AC4" s="141"/>
+      <c r="AD4" s="141"/>
+      <c r="AE4" s="141"/>
       <c r="AF4" s="30"/>
-      <c r="AG4" s="138" t="s">
+      <c r="AG4" s="152" t="s">
         <v>32</v>
       </c>
-      <c r="AH4" s="138"/>
-      <c r="AI4" s="138"/>
-      <c r="AJ4" s="138"/>
-      <c r="AK4" s="138"/>
+      <c r="AH4" s="152"/>
+      <c r="AI4" s="152"/>
+      <c r="AJ4" s="152"/>
+      <c r="AK4" s="152"/>
       <c r="AL4" s="30"/>
       <c r="AM4" s="30"/>
       <c r="AN4" s="30"/>
@@ -11660,7 +11739,7 @@
       </c>
       <c r="C6" s="32" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">IFERROR(IF(MIN(Jalons435[Début])=0,TODAY(),B11(Jalons435[Début])),TODAY())</f>
-        <v>46193</v>
+        <v>46196</v>
       </c>
       <c r="D6" s="48"/>
       <c r="E6" s="30"/>
@@ -11679,7 +11758,7 @@
       <c r="O6" s="88"/>
       <c r="P6" s="88" t="str">
         <f ca="1">IF(TEXT(P7,"mmmm")=I6,"",TEXT(P7,"mmmm"))</f>
-        <v/>
+        <v>juillet</v>
       </c>
       <c r="Q6" s="88"/>
       <c r="R6" s="88"/>
@@ -11689,7 +11768,7 @@
       <c r="V6" s="88"/>
       <c r="W6" s="88" t="str">
         <f ca="1">IF(OR(TEXT(W7,"mmmm")=P6,TEXT(W7,"mmmm")=I6),"",TEXT(W7,"mmmm"))</f>
-        <v>juillet</v>
+        <v/>
       </c>
       <c r="X6" s="88"/>
       <c r="Y6" s="88"/>
@@ -11764,227 +11843,227 @@
       <c r="H7" s="27"/>
       <c r="I7" s="109">
         <f ca="1">IFERROR(Début_Projet+Incrément_de_défilement,TODAY())</f>
-        <v>46194</v>
+        <v>46197</v>
       </c>
       <c r="J7" s="110">
         <f ca="1">I7+1</f>
-        <v>46195</v>
+        <v>46198</v>
       </c>
       <c r="K7" s="110">
         <f t="shared" ref="K7:AX7" ca="1" si="0">J7+1</f>
-        <v>46196</v>
+        <v>46199</v>
       </c>
       <c r="L7" s="110">
         <f t="shared" ca="1" si="0"/>
-        <v>46197</v>
+        <v>46200</v>
       </c>
       <c r="M7" s="110">
         <f t="shared" ca="1" si="0"/>
-        <v>46198</v>
+        <v>46201</v>
       </c>
       <c r="N7" s="110">
         <f t="shared" ca="1" si="0"/>
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="O7" s="111">
         <f t="shared" ca="1" si="0"/>
-        <v>46200</v>
+        <v>46203</v>
       </c>
       <c r="P7" s="110">
         <f ca="1">O7+1</f>
-        <v>46201</v>
+        <v>46204</v>
       </c>
       <c r="Q7" s="110">
         <f ca="1">P7+1</f>
-        <v>46202</v>
+        <v>46205</v>
       </c>
       <c r="R7" s="110">
         <f t="shared" ca="1" si="0"/>
-        <v>46203</v>
+        <v>46206</v>
       </c>
       <c r="S7" s="110">
         <f t="shared" ca="1" si="0"/>
-        <v>46204</v>
+        <v>46207</v>
       </c>
       <c r="T7" s="110">
         <f t="shared" ca="1" si="0"/>
-        <v>46205</v>
+        <v>46208</v>
       </c>
       <c r="U7" s="110">
         <f t="shared" ca="1" si="0"/>
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="V7" s="111">
         <f t="shared" ca="1" si="0"/>
-        <v>46207</v>
+        <v>46210</v>
       </c>
       <c r="W7" s="110">
         <f ca="1">V7+1</f>
-        <v>46208</v>
+        <v>46211</v>
       </c>
       <c r="X7" s="110">
         <f ca="1">W7+1</f>
-        <v>46209</v>
+        <v>46212</v>
       </c>
       <c r="Y7" s="110">
         <f t="shared" ca="1" si="0"/>
-        <v>46210</v>
+        <v>46213</v>
       </c>
       <c r="Z7" s="110">
         <f t="shared" ca="1" si="0"/>
-        <v>46211</v>
+        <v>46214</v>
       </c>
       <c r="AA7" s="110">
         <f t="shared" ca="1" si="0"/>
-        <v>46212</v>
+        <v>46215</v>
       </c>
       <c r="AB7" s="110">
         <f t="shared" ca="1" si="0"/>
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="AC7" s="111">
         <f t="shared" ca="1" si="0"/>
-        <v>46214</v>
+        <v>46217</v>
       </c>
       <c r="AD7" s="110">
         <f ca="1">AC7+1</f>
-        <v>46215</v>
+        <v>46218</v>
       </c>
       <c r="AE7" s="110">
         <f ca="1">AD7+1</f>
-        <v>46216</v>
+        <v>46219</v>
       </c>
       <c r="AF7" s="110">
         <f t="shared" ca="1" si="0"/>
-        <v>46217</v>
+        <v>46220</v>
       </c>
       <c r="AG7" s="110">
         <f t="shared" ca="1" si="0"/>
-        <v>46218</v>
+        <v>46221</v>
       </c>
       <c r="AH7" s="110">
         <f t="shared" ca="1" si="0"/>
-        <v>46219</v>
+        <v>46222</v>
       </c>
       <c r="AI7" s="110">
         <f t="shared" ca="1" si="0"/>
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="AJ7" s="111">
         <f t="shared" ca="1" si="0"/>
-        <v>46221</v>
+        <v>46224</v>
       </c>
       <c r="AK7" s="110">
         <f ca="1">AJ7+1</f>
-        <v>46222</v>
+        <v>46225</v>
       </c>
       <c r="AL7" s="110">
         <f ca="1">AK7+1</f>
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="AM7" s="110">
         <f t="shared" ca="1" si="0"/>
-        <v>46224</v>
+        <v>46227</v>
       </c>
       <c r="AN7" s="110">
         <f t="shared" ca="1" si="0"/>
-        <v>46225</v>
+        <v>46228</v>
       </c>
       <c r="AO7" s="110">
         <f t="shared" ca="1" si="0"/>
-        <v>46226</v>
+        <v>46229</v>
       </c>
       <c r="AP7" s="110">
         <f t="shared" ca="1" si="0"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="AQ7" s="111">
         <f t="shared" ca="1" si="0"/>
-        <v>46228</v>
+        <v>46231</v>
       </c>
       <c r="AR7" s="110">
         <f ca="1">AQ7+1</f>
-        <v>46229</v>
+        <v>46232</v>
       </c>
       <c r="AS7" s="110">
         <f ca="1">AR7+1</f>
-        <v>46230</v>
+        <v>46233</v>
       </c>
       <c r="AT7" s="110">
         <f t="shared" ca="1" si="0"/>
-        <v>46231</v>
+        <v>46234</v>
       </c>
       <c r="AU7" s="110">
         <f t="shared" ca="1" si="0"/>
-        <v>46232</v>
+        <v>46235</v>
       </c>
       <c r="AV7" s="110">
         <f t="shared" ca="1" si="0"/>
-        <v>46233</v>
+        <v>46236</v>
       </c>
       <c r="AW7" s="110">
         <f t="shared" ca="1" si="0"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="AX7" s="111">
         <f t="shared" ca="1" si="0"/>
-        <v>46235</v>
+        <v>46238</v>
       </c>
       <c r="AY7" s="110">
         <f ca="1">AX7+1</f>
-        <v>46236</v>
+        <v>46239</v>
       </c>
       <c r="AZ7" s="110">
         <f ca="1">AY7+1</f>
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="BA7" s="110">
         <f t="shared" ref="BA7:BE7" ca="1" si="1">AZ7+1</f>
-        <v>46238</v>
+        <v>46241</v>
       </c>
       <c r="BB7" s="110">
         <f t="shared" ca="1" si="1"/>
-        <v>46239</v>
+        <v>46242</v>
       </c>
       <c r="BC7" s="110">
         <f t="shared" ca="1" si="1"/>
-        <v>46240</v>
+        <v>46243</v>
       </c>
       <c r="BD7" s="110">
         <f t="shared" ca="1" si="1"/>
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="BE7" s="111">
         <f t="shared" ca="1" si="1"/>
-        <v>46242</v>
+        <v>46245</v>
       </c>
       <c r="BF7" s="110">
         <f ca="1">BE7+1</f>
-        <v>46243</v>
+        <v>46246</v>
       </c>
       <c r="BG7" s="110">
         <f ca="1">BF7+1</f>
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="BH7" s="110">
         <f t="shared" ref="BH7:BL7" ca="1" si="2">BG7+1</f>
-        <v>46245</v>
+        <v>46248</v>
       </c>
       <c r="BI7" s="110">
         <f t="shared" ca="1" si="2"/>
-        <v>46246</v>
+        <v>46249</v>
       </c>
       <c r="BJ7" s="110">
         <f t="shared" ca="1" si="2"/>
-        <v>46247</v>
+        <v>46250</v>
       </c>
       <c r="BK7" s="110">
         <f t="shared" ca="1" si="2"/>
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="BL7" s="112">
         <f t="shared" ca="1" si="2"/>
-        <v>46249</v>
+        <v>46252</v>
       </c>
       <c r="BM7" s="30"/>
     </row>
@@ -12078,227 +12157,227 @@
       <c r="H9" s="43"/>
       <c r="I9" s="35" t="str">
         <f t="shared" ref="I9:AN9" ca="1" si="3">LEFT(TEXT(I7,"jjj"),1)</f>
-        <v>d</v>
+        <v>m</v>
       </c>
       <c r="J9" s="35" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>l</v>
+        <v>j</v>
       </c>
       <c r="K9" s="35" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>m</v>
+        <v>v</v>
       </c>
       <c r="L9" s="35" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>m</v>
+        <v>s</v>
       </c>
       <c r="M9" s="35" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>j</v>
+        <v>d</v>
       </c>
       <c r="N9" s="35" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>v</v>
+        <v>l</v>
       </c>
       <c r="O9" s="35" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>s</v>
+        <v>m</v>
       </c>
       <c r="P9" s="35" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>d</v>
+        <v>m</v>
       </c>
       <c r="Q9" s="35" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>l</v>
+        <v>j</v>
       </c>
       <c r="R9" s="35" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>m</v>
+        <v>v</v>
       </c>
       <c r="S9" s="35" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>m</v>
+        <v>s</v>
       </c>
       <c r="T9" s="35" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>j</v>
+        <v>d</v>
       </c>
       <c r="U9" s="35" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>v</v>
+        <v>l</v>
       </c>
       <c r="V9" s="35" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>s</v>
+        <v>m</v>
       </c>
       <c r="W9" s="35" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>d</v>
+        <v>m</v>
       </c>
       <c r="X9" s="35" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>l</v>
+        <v>j</v>
       </c>
       <c r="Y9" s="35" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>m</v>
+        <v>v</v>
       </c>
       <c r="Z9" s="35" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>m</v>
+        <v>s</v>
       </c>
       <c r="AA9" s="35" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>j</v>
+        <v>d</v>
       </c>
       <c r="AB9" s="35" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>v</v>
+        <v>l</v>
       </c>
       <c r="AC9" s="35" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>s</v>
+        <v>m</v>
       </c>
       <c r="AD9" s="35" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>d</v>
+        <v>m</v>
       </c>
       <c r="AE9" s="35" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>l</v>
+        <v>j</v>
       </c>
       <c r="AF9" s="35" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>m</v>
+        <v>v</v>
       </c>
       <c r="AG9" s="35" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>m</v>
+        <v>s</v>
       </c>
       <c r="AH9" s="35" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>j</v>
+        <v>d</v>
       </c>
       <c r="AI9" s="35" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>v</v>
+        <v>l</v>
       </c>
       <c r="AJ9" s="35" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>s</v>
+        <v>m</v>
       </c>
       <c r="AK9" s="35" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>d</v>
+        <v>m</v>
       </c>
       <c r="AL9" s="35" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>l</v>
+        <v>j</v>
       </c>
       <c r="AM9" s="35" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>m</v>
+        <v>v</v>
       </c>
       <c r="AN9" s="35" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>m</v>
+        <v>s</v>
       </c>
       <c r="AO9" s="35" t="str">
         <f t="shared" ref="AO9:BL9" ca="1" si="4">LEFT(TEXT(AO7,"jjj"),1)</f>
-        <v>j</v>
+        <v>d</v>
       </c>
       <c r="AP9" s="35" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>v</v>
+        <v>l</v>
       </c>
       <c r="AQ9" s="35" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>s</v>
+        <v>m</v>
       </c>
       <c r="AR9" s="35" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>d</v>
+        <v>m</v>
       </c>
       <c r="AS9" s="35" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>l</v>
+        <v>j</v>
       </c>
       <c r="AT9" s="35" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>m</v>
+        <v>v</v>
       </c>
       <c r="AU9" s="35" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>m</v>
+        <v>s</v>
       </c>
       <c r="AV9" s="35" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>j</v>
+        <v>d</v>
       </c>
       <c r="AW9" s="35" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>v</v>
+        <v>l</v>
       </c>
       <c r="AX9" s="35" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>s</v>
+        <v>m</v>
       </c>
       <c r="AY9" s="35" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>d</v>
+        <v>m</v>
       </c>
       <c r="AZ9" s="35" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>l</v>
+        <v>j</v>
       </c>
       <c r="BA9" s="35" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>m</v>
+        <v>v</v>
       </c>
       <c r="BB9" s="35" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>m</v>
+        <v>s</v>
       </c>
       <c r="BC9" s="35" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>j</v>
+        <v>d</v>
       </c>
       <c r="BD9" s="35" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>v</v>
+        <v>l</v>
       </c>
       <c r="BE9" s="35" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>s</v>
+        <v>m</v>
       </c>
       <c r="BF9" s="35" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>d</v>
+        <v>m</v>
       </c>
       <c r="BG9" s="35" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>l</v>
+        <v>j</v>
       </c>
       <c r="BH9" s="35" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>m</v>
+        <v>v</v>
       </c>
       <c r="BI9" s="35" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>m</v>
+        <v>s</v>
       </c>
       <c r="BJ9" s="35" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>j</v>
+        <v>d</v>
       </c>
       <c r="BK9" s="35" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>v</v>
+        <v>l</v>
       </c>
       <c r="BL9" s="35" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>s</v>
+        <v>m</v>
       </c>
       <c r="BM9" s="30"/>
     </row>
@@ -12622,7 +12701,7 @@
       </c>
       <c r="F12" s="21">
         <f ca="1">TODAY()</f>
-        <v>46193</v>
+        <v>46196</v>
       </c>
       <c r="G12" s="22">
         <v>3</v>
@@ -12866,7 +12945,7 @@
       <c r="E13" s="20"/>
       <c r="F13" s="21">
         <f ca="1">TODAY()+5</f>
-        <v>46198</v>
+        <v>46201</v>
       </c>
       <c r="G13" s="22">
         <v>1</v>
@@ -13112,7 +13191,7 @@
       </c>
       <c r="F14" s="21">
         <f ca="1">F12-3</f>
-        <v>46190</v>
+        <v>46193</v>
       </c>
       <c r="G14" s="22">
         <v>10</v>
@@ -13356,7 +13435,7 @@
       <c r="E15" s="20"/>
       <c r="F15" s="21">
         <f ca="1">F12+20</f>
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="G15" s="22">
         <v>1</v>
@@ -13602,7 +13681,7 @@
       </c>
       <c r="F16" s="21">
         <f ca="1">F12+6</f>
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="G16" s="22">
         <v>6</v>
@@ -14085,7 +14164,7 @@
       </c>
       <c r="F18" s="21">
         <f ca="1">F12+6</f>
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="G18" s="22">
         <v>13</v>
@@ -14331,7 +14410,7 @@
       </c>
       <c r="F19" s="21">
         <f ca="1">F18+2</f>
-        <v>46201</v>
+        <v>46204</v>
       </c>
       <c r="G19" s="22">
         <v>9</v>
@@ -14577,7 +14656,7 @@
       </c>
       <c r="F20" s="21">
         <f ca="1">F19+5</f>
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="G20" s="22">
         <v>11</v>
@@ -14821,7 +14900,7 @@
       <c r="E21" s="20"/>
       <c r="F21" s="21">
         <f ca="1">F20+2</f>
-        <v>46208</v>
+        <v>46211</v>
       </c>
       <c r="G21" s="22">
         <v>1</v>
@@ -15063,7 +15142,7 @@
       <c r="E22" s="20"/>
       <c r="F22" s="21">
         <f ca="1">F21+1</f>
-        <v>46209</v>
+        <v>46212</v>
       </c>
       <c r="G22" s="22">
         <v>24</v>
@@ -15544,7 +15623,7 @@
       <c r="E24" s="20"/>
       <c r="F24" s="21">
         <f ca="1">F12+15</f>
-        <v>46208</v>
+        <v>46211</v>
       </c>
       <c r="G24" s="22">
         <v>4</v>
@@ -15788,7 +15867,7 @@
       <c r="E25" s="20"/>
       <c r="F25" s="21">
         <f ca="1">F24+3</f>
-        <v>46211</v>
+        <v>46214</v>
       </c>
       <c r="G25" s="22">
         <v>14</v>
@@ -16032,7 +16111,7 @@
       <c r="E26" s="20"/>
       <c r="F26" s="21">
         <f ca="1">F25+15</f>
-        <v>46226</v>
+        <v>46229</v>
       </c>
       <c r="G26" s="22">
         <v>6</v>
@@ -16276,7 +16355,7 @@
       <c r="E27" s="20"/>
       <c r="F27" s="21">
         <f ca="1">F21+22</f>
-        <v>46230</v>
+        <v>46233</v>
       </c>
       <c r="G27" s="22">
         <v>3</v>
@@ -16520,7 +16599,7 @@
       <c r="E28" s="20"/>
       <c r="F28" s="21">
         <f ca="1">F16</f>
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="G28" s="22">
         <v>19</v>
@@ -16999,7 +17078,7 @@
       <c r="E30" s="20"/>
       <c r="F30" s="21">
         <f ca="1">F27+3</f>
-        <v>46233</v>
+        <v>46236</v>
       </c>
       <c r="G30" s="22">
         <v>15</v>
@@ -17241,7 +17320,7 @@
       <c r="E31" s="20"/>
       <c r="F31" s="21">
         <f ca="1">F30+14</f>
-        <v>46247</v>
+        <v>46250</v>
       </c>
       <c r="G31" s="22">
         <v>5</v>
@@ -17485,7 +17564,7 @@
       <c r="E32" s="20"/>
       <c r="F32" s="21">
         <f ca="1">F31+42</f>
-        <v>46289</v>
+        <v>46292</v>
       </c>
       <c r="G32" s="22">
         <v>1</v>
@@ -18529,39 +18608,39 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I6:AM6">
-    <cfRule type="expression" dxfId="25" priority="4">
+    <cfRule type="expression" dxfId="17" priority="4">
       <formula>I$7&lt;=EOMONTH($I$7,0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I6:BL6">
-    <cfRule type="expression" dxfId="24" priority="2">
+    <cfRule type="expression" dxfId="16" priority="2">
       <formula>AND(I$7&lt;=EOMONTH($I$7,1),I$7&gt;EOMONTH($I$7,0))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I7:BL36">
-    <cfRule type="expression" dxfId="23" priority="1">
+    <cfRule type="expression" dxfId="15" priority="1">
       <formula>AND(TODAY()&gt;=I$7,TODAY()&lt;J$7)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I10:BL35">
-    <cfRule type="expression" dxfId="22" priority="7" stopIfTrue="1">
+    <cfRule type="expression" dxfId="14" priority="7" stopIfTrue="1">
       <formula>AND($C10="Risque faible",I$7&gt;=$F10,I$7&lt;=$F10+$G10-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="8" stopIfTrue="1">
+    <cfRule type="expression" dxfId="13" priority="8" stopIfTrue="1">
       <formula>AND($C10="Risque élevé",I$7&gt;=$F10,I$7&lt;=$F10+$G10-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="9" stopIfTrue="1">
+    <cfRule type="expression" dxfId="12" priority="9" stopIfTrue="1">
       <formula>AND($C10="En bonne voie",I$7&gt;=$F10,I$7&lt;=$F10+$G10-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="19" priority="10" stopIfTrue="1">
+    <cfRule type="expression" dxfId="11" priority="10" stopIfTrue="1">
       <formula>AND($C10="Risque moyen",I$7&gt;=$F10,I$7&lt;=$F10+$G10-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="11" stopIfTrue="1">
+    <cfRule type="expression" dxfId="10" priority="11" stopIfTrue="1">
       <formula>AND(LEN($C10)=0,I$7&gt;=$F10,I$7&lt;=$F10+$G10-1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J6:BL6">
-    <cfRule type="expression" dxfId="17" priority="3">
+    <cfRule type="expression" dxfId="9" priority="3">
       <formula>AND(J$7&lt;=EOMONTH($I$7,2),J$7&gt;EOMONTH($I$7,0),J$7&gt;EOMONTH($I$7,1))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18703,27 +18782,27 @@
     <row r="1" spans="1:68" ht="25.15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="1:68" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="10"/>
-      <c r="B2" s="139" t="s">
+      <c r="B2" s="153" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="139"/>
-      <c r="D2" s="139"/>
-      <c r="E2" s="139"/>
-      <c r="F2" s="139"/>
-      <c r="G2" s="139"/>
-      <c r="H2" s="139"/>
-      <c r="I2" s="140"/>
-      <c r="J2" s="140"/>
-      <c r="K2" s="140"/>
-      <c r="L2" s="140"/>
-      <c r="M2" s="140"/>
-      <c r="N2" s="140"/>
-      <c r="O2" s="141"/>
-      <c r="P2" s="141"/>
-      <c r="Q2" s="141"/>
-      <c r="R2" s="141"/>
-      <c r="S2" s="141"/>
-      <c r="T2" s="141"/>
+      <c r="C2" s="153"/>
+      <c r="D2" s="153"/>
+      <c r="E2" s="153"/>
+      <c r="F2" s="153"/>
+      <c r="G2" s="153"/>
+      <c r="H2" s="153"/>
+      <c r="I2" s="154"/>
+      <c r="J2" s="154"/>
+      <c r="K2" s="154"/>
+      <c r="L2" s="154"/>
+      <c r="M2" s="154"/>
+      <c r="N2" s="154"/>
+      <c r="O2" s="155"/>
+      <c r="P2" s="155"/>
+      <c r="Q2" s="155"/>
+      <c r="R2" s="155"/>
+      <c r="S2" s="155"/>
+      <c r="T2" s="155"/>
       <c r="U2" s="90"/>
       <c r="V2" s="90"/>
       <c r="W2" s="90"/>
@@ -18797,41 +18876,41 @@
         <v>30</v>
       </c>
       <c r="H4" s="69"/>
-      <c r="I4" s="132" t="s">
+      <c r="I4" s="146" t="s">
         <v>25</v>
       </c>
-      <c r="J4" s="132"/>
-      <c r="K4" s="132"/>
-      <c r="L4" s="132"/>
-      <c r="M4" s="132"/>
-      <c r="O4" s="133" t="s">
+      <c r="J4" s="146"/>
+      <c r="K4" s="146"/>
+      <c r="L4" s="146"/>
+      <c r="M4" s="146"/>
+      <c r="O4" s="147" t="s">
         <v>22</v>
       </c>
-      <c r="P4" s="133"/>
-      <c r="Q4" s="133"/>
-      <c r="R4" s="133"/>
-      <c r="S4" s="133"/>
-      <c r="U4" s="126" t="s">
+      <c r="P4" s="147"/>
+      <c r="Q4" s="147"/>
+      <c r="R4" s="147"/>
+      <c r="S4" s="147"/>
+      <c r="U4" s="140" t="s">
         <v>23</v>
       </c>
-      <c r="V4" s="126"/>
-      <c r="W4" s="126"/>
-      <c r="X4" s="126"/>
-      <c r="Y4" s="126"/>
-      <c r="AA4" s="127" t="s">
+      <c r="V4" s="140"/>
+      <c r="W4" s="140"/>
+      <c r="X4" s="140"/>
+      <c r="Y4" s="140"/>
+      <c r="AA4" s="141" t="s">
         <v>24</v>
       </c>
-      <c r="AB4" s="127"/>
-      <c r="AC4" s="127"/>
-      <c r="AD4" s="127"/>
-      <c r="AE4" s="127"/>
-      <c r="AG4" s="138" t="s">
+      <c r="AB4" s="141"/>
+      <c r="AC4" s="141"/>
+      <c r="AD4" s="141"/>
+      <c r="AE4" s="141"/>
+      <c r="AG4" s="152" t="s">
         <v>32</v>
       </c>
-      <c r="AH4" s="138"/>
-      <c r="AI4" s="138"/>
-      <c r="AJ4" s="138"/>
-      <c r="AK4" s="138"/>
+      <c r="AH4" s="152"/>
+      <c r="AI4" s="152"/>
+      <c r="AJ4" s="152"/>
+      <c r="AK4" s="152"/>
     </row>
     <row r="5" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="10"/>
@@ -18852,7 +18931,7 @@
       </c>
       <c r="C6" s="74" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">IFERROR(IF(MIN(Jalons43524[Début])=0,TODAY(),B11(Jalons43524[Début])),TODAY())</f>
-        <v>46193</v>
+        <v>46196</v>
       </c>
       <c r="D6" s="75"/>
       <c r="E6" s="69"/>
@@ -18871,7 +18950,7 @@
       <c r="O6" s="85"/>
       <c r="P6" s="85" t="str">
         <f ca="1">IF(TEXT(P7,"mmmm")=I6,"",TEXT(P7,"mmmm"))</f>
-        <v/>
+        <v>juillet</v>
       </c>
       <c r="Q6" s="85"/>
       <c r="R6" s="85"/>
@@ -18881,7 +18960,7 @@
       <c r="V6" s="85"/>
       <c r="W6" s="85" t="str">
         <f ca="1">IF(OR(TEXT(W7,"mmmm")=P6,TEXT(W7,"mmmm")=I6),"",TEXT(W7,"mmmm"))</f>
-        <v>juillet</v>
+        <v/>
       </c>
       <c r="X6" s="85"/>
       <c r="Y6" s="85"/>
@@ -18955,227 +19034,227 @@
       <c r="H7" s="77"/>
       <c r="I7" s="116">
         <f ca="1">IFERROR(Début_Projet+Incrément_de_défilement,TODAY())</f>
-        <v>46194</v>
+        <v>46197</v>
       </c>
       <c r="J7" s="117">
         <f ca="1">I7+1</f>
-        <v>46195</v>
+        <v>46198</v>
       </c>
       <c r="K7" s="117">
         <f t="shared" ref="K7:AX7" ca="1" si="0">J7+1</f>
-        <v>46196</v>
+        <v>46199</v>
       </c>
       <c r="L7" s="117">
         <f t="shared" ca="1" si="0"/>
-        <v>46197</v>
+        <v>46200</v>
       </c>
       <c r="M7" s="117">
         <f t="shared" ca="1" si="0"/>
-        <v>46198</v>
+        <v>46201</v>
       </c>
       <c r="N7" s="117">
         <f t="shared" ca="1" si="0"/>
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="O7" s="118">
         <f t="shared" ca="1" si="0"/>
-        <v>46200</v>
+        <v>46203</v>
       </c>
       <c r="P7" s="117">
         <f ca="1">O7+1</f>
-        <v>46201</v>
+        <v>46204</v>
       </c>
       <c r="Q7" s="117">
         <f ca="1">P7+1</f>
-        <v>46202</v>
+        <v>46205</v>
       </c>
       <c r="R7" s="117">
         <f t="shared" ca="1" si="0"/>
-        <v>46203</v>
+        <v>46206</v>
       </c>
       <c r="S7" s="117">
         <f t="shared" ca="1" si="0"/>
-        <v>46204</v>
+        <v>46207</v>
       </c>
       <c r="T7" s="117">
         <f t="shared" ca="1" si="0"/>
-        <v>46205</v>
+        <v>46208</v>
       </c>
       <c r="U7" s="117">
         <f t="shared" ca="1" si="0"/>
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="V7" s="118">
         <f t="shared" ca="1" si="0"/>
-        <v>46207</v>
+        <v>46210</v>
       </c>
       <c r="W7" s="117">
         <f ca="1">V7+1</f>
-        <v>46208</v>
+        <v>46211</v>
       </c>
       <c r="X7" s="117">
         <f ca="1">W7+1</f>
-        <v>46209</v>
+        <v>46212</v>
       </c>
       <c r="Y7" s="117">
         <f t="shared" ca="1" si="0"/>
-        <v>46210</v>
+        <v>46213</v>
       </c>
       <c r="Z7" s="117">
         <f t="shared" ca="1" si="0"/>
-        <v>46211</v>
+        <v>46214</v>
       </c>
       <c r="AA7" s="117">
         <f t="shared" ca="1" si="0"/>
-        <v>46212</v>
+        <v>46215</v>
       </c>
       <c r="AB7" s="117">
         <f t="shared" ca="1" si="0"/>
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="AC7" s="118">
         <f t="shared" ca="1" si="0"/>
-        <v>46214</v>
+        <v>46217</v>
       </c>
       <c r="AD7" s="117">
         <f ca="1">AC7+1</f>
-        <v>46215</v>
+        <v>46218</v>
       </c>
       <c r="AE7" s="117">
         <f ca="1">AD7+1</f>
-        <v>46216</v>
+        <v>46219</v>
       </c>
       <c r="AF7" s="117">
         <f t="shared" ca="1" si="0"/>
-        <v>46217</v>
+        <v>46220</v>
       </c>
       <c r="AG7" s="117">
         <f t="shared" ca="1" si="0"/>
-        <v>46218</v>
+        <v>46221</v>
       </c>
       <c r="AH7" s="117">
         <f t="shared" ca="1" si="0"/>
-        <v>46219</v>
+        <v>46222</v>
       </c>
       <c r="AI7" s="117">
         <f t="shared" ca="1" si="0"/>
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="AJ7" s="118">
         <f t="shared" ca="1" si="0"/>
-        <v>46221</v>
+        <v>46224</v>
       </c>
       <c r="AK7" s="117">
         <f ca="1">AJ7+1</f>
-        <v>46222</v>
+        <v>46225</v>
       </c>
       <c r="AL7" s="117">
         <f ca="1">AK7+1</f>
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="AM7" s="117">
         <f t="shared" ca="1" si="0"/>
-        <v>46224</v>
+        <v>46227</v>
       </c>
       <c r="AN7" s="117">
         <f t="shared" ca="1" si="0"/>
-        <v>46225</v>
+        <v>46228</v>
       </c>
       <c r="AO7" s="117">
         <f t="shared" ca="1" si="0"/>
-        <v>46226</v>
+        <v>46229</v>
       </c>
       <c r="AP7" s="117">
         <f t="shared" ca="1" si="0"/>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="AQ7" s="118">
         <f t="shared" ca="1" si="0"/>
-        <v>46228</v>
+        <v>46231</v>
       </c>
       <c r="AR7" s="117">
         <f ca="1">AQ7+1</f>
-        <v>46229</v>
+        <v>46232</v>
       </c>
       <c r="AS7" s="117">
         <f ca="1">AR7+1</f>
-        <v>46230</v>
+        <v>46233</v>
       </c>
       <c r="AT7" s="117">
         <f t="shared" ca="1" si="0"/>
-        <v>46231</v>
+        <v>46234</v>
       </c>
       <c r="AU7" s="117">
         <f t="shared" ca="1" si="0"/>
-        <v>46232</v>
+        <v>46235</v>
       </c>
       <c r="AV7" s="117">
         <f t="shared" ca="1" si="0"/>
-        <v>46233</v>
+        <v>46236</v>
       </c>
       <c r="AW7" s="117">
         <f t="shared" ca="1" si="0"/>
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="AX7" s="118">
         <f t="shared" ca="1" si="0"/>
-        <v>46235</v>
+        <v>46238</v>
       </c>
       <c r="AY7" s="117">
         <f ca="1">AX7+1</f>
-        <v>46236</v>
+        <v>46239</v>
       </c>
       <c r="AZ7" s="117">
         <f ca="1">AY7+1</f>
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="BA7" s="117">
         <f t="shared" ref="BA7:BE7" ca="1" si="1">AZ7+1</f>
-        <v>46238</v>
+        <v>46241</v>
       </c>
       <c r="BB7" s="117">
         <f t="shared" ca="1" si="1"/>
-        <v>46239</v>
+        <v>46242</v>
       </c>
       <c r="BC7" s="117">
         <f t="shared" ca="1" si="1"/>
-        <v>46240</v>
+        <v>46243</v>
       </c>
       <c r="BD7" s="117">
         <f t="shared" ca="1" si="1"/>
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="BE7" s="118">
         <f t="shared" ca="1" si="1"/>
-        <v>46242</v>
+        <v>46245</v>
       </c>
       <c r="BF7" s="117">
         <f ca="1">BE7+1</f>
-        <v>46243</v>
+        <v>46246</v>
       </c>
       <c r="BG7" s="117">
         <f ca="1">BF7+1</f>
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="BH7" s="117">
         <f t="shared" ref="BH7:BL7" ca="1" si="2">BG7+1</f>
-        <v>46245</v>
+        <v>46248</v>
       </c>
       <c r="BI7" s="117">
         <f t="shared" ca="1" si="2"/>
-        <v>46246</v>
+        <v>46249</v>
       </c>
       <c r="BJ7" s="117">
         <f t="shared" ca="1" si="2"/>
-        <v>46247</v>
+        <v>46250</v>
       </c>
       <c r="BK7" s="117">
         <f t="shared" ca="1" si="2"/>
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="BL7" s="118">
         <f t="shared" ca="1" si="2"/>
-        <v>46249</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="8" spans="1:68" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -19267,227 +19346,227 @@
       <c r="H9" s="82"/>
       <c r="I9" s="91" t="str">
         <f t="shared" ref="I9:AN9" ca="1" si="3">LEFT(TEXT(I7,"jjj"),1)</f>
-        <v>d</v>
+        <v>m</v>
       </c>
       <c r="J9" s="91" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>l</v>
+        <v>j</v>
       </c>
       <c r="K9" s="91" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>m</v>
+        <v>v</v>
       </c>
       <c r="L9" s="91" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>m</v>
+        <v>s</v>
       </c>
       <c r="M9" s="91" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>j</v>
+        <v>d</v>
       </c>
       <c r="N9" s="91" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>v</v>
+        <v>l</v>
       </c>
       <c r="O9" s="91" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>s</v>
+        <v>m</v>
       </c>
       <c r="P9" s="91" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>d</v>
+        <v>m</v>
       </c>
       <c r="Q9" s="91" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>l</v>
+        <v>j</v>
       </c>
       <c r="R9" s="91" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>m</v>
+        <v>v</v>
       </c>
       <c r="S9" s="91" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>m</v>
+        <v>s</v>
       </c>
       <c r="T9" s="91" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>j</v>
+        <v>d</v>
       </c>
       <c r="U9" s="91" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>v</v>
+        <v>l</v>
       </c>
       <c r="V9" s="91" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>s</v>
+        <v>m</v>
       </c>
       <c r="W9" s="91" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>d</v>
+        <v>m</v>
       </c>
       <c r="X9" s="91" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>l</v>
+        <v>j</v>
       </c>
       <c r="Y9" s="91" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>m</v>
+        <v>v</v>
       </c>
       <c r="Z9" s="91" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>m</v>
+        <v>s</v>
       </c>
       <c r="AA9" s="91" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>j</v>
+        <v>d</v>
       </c>
       <c r="AB9" s="91" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>v</v>
+        <v>l</v>
       </c>
       <c r="AC9" s="91" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>s</v>
+        <v>m</v>
       </c>
       <c r="AD9" s="91" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>d</v>
+        <v>m</v>
       </c>
       <c r="AE9" s="91" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>l</v>
+        <v>j</v>
       </c>
       <c r="AF9" s="91" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>m</v>
+        <v>v</v>
       </c>
       <c r="AG9" s="91" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>m</v>
+        <v>s</v>
       </c>
       <c r="AH9" s="91" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>j</v>
+        <v>d</v>
       </c>
       <c r="AI9" s="91" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>v</v>
+        <v>l</v>
       </c>
       <c r="AJ9" s="91" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>s</v>
+        <v>m</v>
       </c>
       <c r="AK9" s="91" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>d</v>
+        <v>m</v>
       </c>
       <c r="AL9" s="91" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>l</v>
+        <v>j</v>
       </c>
       <c r="AM9" s="91" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>m</v>
+        <v>v</v>
       </c>
       <c r="AN9" s="91" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>m</v>
+        <v>s</v>
       </c>
       <c r="AO9" s="91" t="str">
         <f t="shared" ref="AO9:BL9" ca="1" si="4">LEFT(TEXT(AO7,"jjj"),1)</f>
-        <v>j</v>
+        <v>d</v>
       </c>
       <c r="AP9" s="91" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>v</v>
+        <v>l</v>
       </c>
       <c r="AQ9" s="91" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>s</v>
+        <v>m</v>
       </c>
       <c r="AR9" s="91" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>d</v>
+        <v>m</v>
       </c>
       <c r="AS9" s="91" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>l</v>
+        <v>j</v>
       </c>
       <c r="AT9" s="91" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>m</v>
+        <v>v</v>
       </c>
       <c r="AU9" s="91" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>m</v>
+        <v>s</v>
       </c>
       <c r="AV9" s="91" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>j</v>
+        <v>d</v>
       </c>
       <c r="AW9" s="91" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>v</v>
+        <v>l</v>
       </c>
       <c r="AX9" s="91" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>s</v>
+        <v>m</v>
       </c>
       <c r="AY9" s="91" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>d</v>
+        <v>m</v>
       </c>
       <c r="AZ9" s="91" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>l</v>
+        <v>j</v>
       </c>
       <c r="BA9" s="91" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>m</v>
+        <v>v</v>
       </c>
       <c r="BB9" s="91" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>m</v>
+        <v>s</v>
       </c>
       <c r="BC9" s="91" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>j</v>
+        <v>d</v>
       </c>
       <c r="BD9" s="91" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>v</v>
+        <v>l</v>
       </c>
       <c r="BE9" s="91" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>s</v>
+        <v>m</v>
       </c>
       <c r="BF9" s="91" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>d</v>
+        <v>m</v>
       </c>
       <c r="BG9" s="91" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>l</v>
+        <v>j</v>
       </c>
       <c r="BH9" s="91" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>m</v>
+        <v>v</v>
       </c>
       <c r="BI9" s="91" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>m</v>
+        <v>s</v>
       </c>
       <c r="BJ9" s="91" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>j</v>
+        <v>d</v>
       </c>
       <c r="BK9" s="91" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>v</v>
+        <v>l</v>
       </c>
       <c r="BL9" s="91" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>s</v>
+        <v>m</v>
       </c>
     </row>
     <row r="10" spans="1:68" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
@@ -19807,7 +19886,7 @@
       </c>
       <c r="F12" s="56">
         <f ca="1">TODAY()</f>
-        <v>46193</v>
+        <v>46196</v>
       </c>
       <c r="G12" s="57">
         <v>3</v>
@@ -20050,7 +20129,7 @@
       <c r="E13" s="55"/>
       <c r="F13" s="56">
         <f ca="1">TODAY()+5</f>
-        <v>46198</v>
+        <v>46201</v>
       </c>
       <c r="G13" s="57">
         <v>1</v>
@@ -20295,7 +20374,7 @@
       </c>
       <c r="F14" s="56">
         <f ca="1">F12-3</f>
-        <v>46190</v>
+        <v>46193</v>
       </c>
       <c r="G14" s="57">
         <v>10</v>
@@ -20538,7 +20617,7 @@
       <c r="E15" s="55"/>
       <c r="F15" s="56">
         <f ca="1">F12+20</f>
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="G15" s="57">
         <v>1</v>
@@ -20783,7 +20862,7 @@
       </c>
       <c r="F16" s="56">
         <f ca="1">F12+6</f>
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="G16" s="57">
         <v>6</v>
@@ -21264,7 +21343,7 @@
       </c>
       <c r="F18" s="56">
         <f ca="1">F12+6</f>
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="G18" s="57">
         <v>13</v>
@@ -21509,7 +21588,7 @@
       </c>
       <c r="F19" s="56">
         <f ca="1">F18+2</f>
-        <v>46201</v>
+        <v>46204</v>
       </c>
       <c r="G19" s="57">
         <v>9</v>
@@ -21754,7 +21833,7 @@
       </c>
       <c r="F20" s="56">
         <f ca="1">F19+5</f>
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="G20" s="57">
         <v>11</v>
@@ -21997,7 +22076,7 @@
       <c r="E21" s="55"/>
       <c r="F21" s="56">
         <f ca="1">F20+2</f>
-        <v>46208</v>
+        <v>46211</v>
       </c>
       <c r="G21" s="57">
         <v>1</v>
@@ -22238,7 +22317,7 @@
       <c r="E22" s="55"/>
       <c r="F22" s="56">
         <f ca="1">F21+1</f>
-        <v>46209</v>
+        <v>46212</v>
       </c>
       <c r="G22" s="57">
         <v>24</v>
@@ -22717,7 +22796,7 @@
       <c r="E24" s="55"/>
       <c r="F24" s="56">
         <f ca="1">F12+15</f>
-        <v>46208</v>
+        <v>46211</v>
       </c>
       <c r="G24" s="57">
         <v>4</v>
@@ -22960,7 +23039,7 @@
       <c r="E25" s="55"/>
       <c r="F25" s="56">
         <f ca="1">F24+3</f>
-        <v>46211</v>
+        <v>46214</v>
       </c>
       <c r="G25" s="57">
         <v>14</v>
@@ -23203,7 +23282,7 @@
       <c r="E26" s="55"/>
       <c r="F26" s="56">
         <f ca="1">F25+15</f>
-        <v>46226</v>
+        <v>46229</v>
       </c>
       <c r="G26" s="57">
         <v>6</v>
@@ -23446,7 +23525,7 @@
       <c r="E27" s="55"/>
       <c r="F27" s="56">
         <f ca="1">F21+22</f>
-        <v>46230</v>
+        <v>46233</v>
       </c>
       <c r="G27" s="57">
         <v>3</v>
@@ -23689,7 +23768,7 @@
       <c r="E28" s="55"/>
       <c r="F28" s="56">
         <f ca="1">F16</f>
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="G28" s="57">
         <v>19</v>
@@ -24166,7 +24245,7 @@
       <c r="E30" s="55"/>
       <c r="F30" s="56">
         <f ca="1">F27+3</f>
-        <v>46233</v>
+        <v>46236</v>
       </c>
       <c r="G30" s="57">
         <v>15</v>
@@ -24407,7 +24486,7 @@
       <c r="E31" s="55"/>
       <c r="F31" s="56">
         <f ca="1">F30+14</f>
-        <v>46247</v>
+        <v>46250</v>
       </c>
       <c r="G31" s="57">
         <v>5</v>
@@ -24650,7 +24729,7 @@
       <c r="E32" s="55"/>
       <c r="F32" s="56">
         <f ca="1">F31+42</f>
-        <v>46289</v>
+        <v>46292</v>
       </c>
       <c r="G32" s="57">
         <v>1</v>
@@ -25690,39 +25769,39 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I6:AM6">
-    <cfRule type="expression" dxfId="16" priority="4">
+    <cfRule type="expression" dxfId="8" priority="4">
       <formula>I$7&lt;=EOMONTH($I$7,0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I6:BL6">
-    <cfRule type="expression" dxfId="15" priority="2">
+    <cfRule type="expression" dxfId="7" priority="2">
       <formula>AND(I$7&lt;=EOMONTH($I$7,1),I$7&gt;EOMONTH($I$7,0))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I7:BL36">
-    <cfRule type="expression" dxfId="14" priority="1">
+    <cfRule type="expression" dxfId="6" priority="1">
       <formula>AND(TODAY()&gt;=I$7,TODAY()&lt;J$7)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I10:BL35">
-    <cfRule type="expression" dxfId="13" priority="7" stopIfTrue="1">
+    <cfRule type="expression" dxfId="5" priority="7" stopIfTrue="1">
       <formula>AND($C10="Risque faible",I$7&gt;=$F10,I$7&lt;=$F10+$G10-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="8" stopIfTrue="1">
+    <cfRule type="expression" dxfId="4" priority="8" stopIfTrue="1">
       <formula>AND($C10="Risque élevé",I$7&gt;=$F10,I$7&lt;=$F10+$G10-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="11" priority="9" stopIfTrue="1">
+    <cfRule type="expression" dxfId="3" priority="9" stopIfTrue="1">
       <formula>AND($C10="En bonne voie",I$7&gt;=$F10,I$7&lt;=$F10+$G10-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="10" stopIfTrue="1">
+    <cfRule type="expression" dxfId="2" priority="10" stopIfTrue="1">
       <formula>AND($C10="Risque moyen",I$7&gt;=$F10,I$7&lt;=$F10+$G10-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="11" stopIfTrue="1">
+    <cfRule type="expression" dxfId="1" priority="11" stopIfTrue="1">
       <formula>AND(LEN($C10)=0,I$7&gt;=$F10,I$7&lt;=$F10+$G10-1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J6:BL6">
-    <cfRule type="expression" dxfId="8" priority="3">
+    <cfRule type="expression" dxfId="0" priority="3">
       <formula>AND(J$7&lt;=EOMONTH($I$7,2),J$7&gt;EOMONTH($I$7,0),J$7&gt;EOMONTH($I$7,1))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -25845,12 +25924,22 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </Image>
+    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -26130,28 +26219,22 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </Image>
-    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
-    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39060724-9CA2-4290-8A0C-B53624A594E7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA4BA2A8-DB97-40F9-8DB6-154C09C7467C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
+    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -26178,13 +26261,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA4BA2A8-DB97-40F9-8DB6-154C09C7467C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39060724-9CA2-4290-8A0C-B53624A594E7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
-    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>